--- a/data/targets_new_total.xlsx
+++ b/data/targets_new_total.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAPL02289\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319F9232-8106-4B03-89B0-23BB03A18A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4D8BB6-8374-409A-9C1F-44A6BDB56805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5076,13 +5076,13 @@
         <v>0</v>
       </c>
       <c r="I134" s="7">
-        <v>83.2</v>
+        <v>55.4</v>
       </c>
       <c r="J134" s="7">
-        <v>29.6</v>
+        <v>19.7</v>
       </c>
       <c r="K134" s="7">
-        <v>20.9</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.35">
@@ -5108,16 +5108,16 @@
         <v>0</v>
       </c>
       <c r="H135" s="7">
-        <v>70.7</v>
+        <v>44.7</v>
       </c>
       <c r="I135" s="7">
-        <v>3525.7</v>
+        <v>2289.3000000000002</v>
       </c>
       <c r="J135" s="7">
-        <v>2009.6</v>
+        <v>1307.4000000000001</v>
       </c>
       <c r="K135" s="7">
-        <v>998</v>
+        <v>647.5</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.35">
@@ -5143,16 +5143,16 @@
         <v>0</v>
       </c>
       <c r="H136" s="7">
-        <v>23.6</v>
+        <v>15.9</v>
       </c>
       <c r="I136" s="7">
-        <v>145.4</v>
+        <v>97.7</v>
       </c>
       <c r="J136" s="7">
-        <v>132.9</v>
+        <v>87.8</v>
       </c>
       <c r="K136" s="7">
-        <v>142.1</v>
+        <v>95.4</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.35">
@@ -5222,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="K138" s="7">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.35">
@@ -5245,19 +5245,19 @@
         <v>13</v>
       </c>
       <c r="G139" s="7">
-        <v>1742.1</v>
+        <v>1121.9000000000001</v>
       </c>
       <c r="H139" s="7">
-        <v>674.7</v>
+        <v>437.4</v>
       </c>
       <c r="I139" s="7">
-        <v>466.7</v>
+        <v>300</v>
       </c>
       <c r="J139" s="7">
-        <v>505.1</v>
+        <v>327.2</v>
       </c>
       <c r="K139" s="7">
-        <v>1783.2</v>
+        <v>1144.7</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.35">
@@ -5280,19 +5280,19 @@
         <v>17</v>
       </c>
       <c r="G140" s="7">
-        <v>61.1</v>
+        <v>40.6</v>
       </c>
       <c r="H140" s="7">
-        <v>105.3</v>
+        <v>67.2</v>
       </c>
       <c r="I140" s="7">
-        <v>28.2</v>
+        <v>19.3</v>
       </c>
       <c r="J140" s="7">
-        <v>1534.1</v>
+        <v>992.6</v>
       </c>
       <c r="K140" s="7">
-        <v>1781.3</v>
+        <v>1171.0999999999999</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.35">
@@ -5350,19 +5350,19 @@
         <v>29</v>
       </c>
       <c r="G142" s="7">
-        <v>144.6</v>
+        <v>93.2</v>
       </c>
       <c r="H142" s="7">
-        <v>56.2</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="I142" s="7">
-        <v>24.2</v>
+        <v>16.8</v>
       </c>
       <c r="J142" s="7">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K142" s="7">
-        <v>201.1</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.35">
@@ -5525,7 +5525,7 @@
         <v>29</v>
       </c>
       <c r="G147" s="7">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="H147" s="7">
         <v>0</v>
@@ -5633,16 +5633,16 @@
         <v>0</v>
       </c>
       <c r="H150" s="7">
-        <v>3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I150" s="7">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J150" s="7">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="K150" s="7">
-        <v>11.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.35">
@@ -5665,19 +5665,19 @@
         <v>13</v>
       </c>
       <c r="G151" s="7">
-        <v>37782.800000000003</v>
+        <v>26239.5</v>
       </c>
       <c r="H151" s="7">
-        <v>29938.9</v>
+        <v>20664</v>
       </c>
       <c r="I151" s="7">
-        <v>31091.8</v>
+        <v>21006.7</v>
       </c>
       <c r="J151" s="7">
-        <v>42492.4</v>
+        <v>29094.9</v>
       </c>
       <c r="K151" s="7">
-        <v>57833.7</v>
+        <v>40047</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.35">
@@ -5700,19 +5700,19 @@
         <v>17</v>
       </c>
       <c r="G152" s="7">
-        <v>25376.9</v>
+        <v>16889</v>
       </c>
       <c r="H152" s="7">
-        <v>14223.7</v>
+        <v>9166</v>
       </c>
       <c r="I152" s="7">
-        <v>21901</v>
+        <v>14063.1</v>
       </c>
       <c r="J152" s="7">
-        <v>17198.7</v>
+        <v>11115</v>
       </c>
       <c r="K152" s="7">
-        <v>11684.1</v>
+        <v>7534.8</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.35">
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="H153" s="7">
-        <v>4871.1000000000004</v>
+        <v>3571.7</v>
       </c>
       <c r="I153" s="7">
-        <v>15194.4</v>
+        <v>10148.6</v>
       </c>
       <c r="J153" s="7">
-        <v>1849.7</v>
+        <v>1237.0999999999999</v>
       </c>
       <c r="K153" s="7">
-        <v>12668</v>
+        <v>8584.4</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.35">
@@ -5805,10 +5805,10 @@
         <v>33</v>
       </c>
       <c r="G155" s="7">
-        <v>7748</v>
+        <v>5654.4</v>
       </c>
       <c r="H155" s="7">
-        <v>4973</v>
+        <v>3634.4</v>
       </c>
       <c r="I155" s="7">
         <v>0</v>
@@ -5840,10 +5840,10 @@
         <v>40</v>
       </c>
       <c r="G156" s="7">
-        <v>2877.6</v>
+        <v>2016.6</v>
       </c>
       <c r="H156" s="7">
-        <v>4870.7</v>
+        <v>3359.6</v>
       </c>
       <c r="I156" s="7">
         <v>0</v>
@@ -5875,19 +5875,19 @@
         <v>29</v>
       </c>
       <c r="G157" s="7">
-        <v>7094</v>
+        <v>5217.6000000000004</v>
       </c>
       <c r="H157" s="7">
-        <v>7360.1</v>
+        <v>5411.5</v>
       </c>
       <c r="I157" s="7">
-        <v>2014.8</v>
+        <v>1488.8</v>
       </c>
       <c r="J157" s="7">
-        <v>2450.1999999999998</v>
+        <v>1649.2</v>
       </c>
       <c r="K157" s="7">
-        <v>5159.1000000000004</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.35">
@@ -5913,16 +5913,16 @@
         <v>0</v>
       </c>
       <c r="H158" s="7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I158" s="7">
         <v>0</v>
       </c>
       <c r="J158" s="7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="K158" s="7">
-        <v>13.7</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.35">
@@ -5945,19 +5945,19 @@
         <v>13</v>
       </c>
       <c r="G159" s="7">
-        <v>17110.900000000001</v>
+        <v>11279.9</v>
       </c>
       <c r="H159" s="7">
-        <v>18092</v>
+        <v>12031.4</v>
       </c>
       <c r="I159" s="7">
-        <v>12179.5</v>
+        <v>8043.7</v>
       </c>
       <c r="J159" s="7">
-        <v>16983.400000000001</v>
+        <v>11179.7</v>
       </c>
       <c r="K159" s="7">
-        <v>8941.9</v>
+        <v>5953.5</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.35">
@@ -5980,19 +5980,19 @@
         <v>17</v>
       </c>
       <c r="G160" s="7">
-        <v>30528</v>
+        <v>19705.3</v>
       </c>
       <c r="H160" s="7">
-        <v>19536.599999999999</v>
+        <v>12338.8</v>
       </c>
       <c r="I160" s="7">
-        <v>36144.699999999997</v>
+        <v>22771.7</v>
       </c>
       <c r="J160" s="7">
-        <v>26277.3</v>
+        <v>16580.2</v>
       </c>
       <c r="K160" s="7">
-        <v>24092.1</v>
+        <v>15239</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.35">
@@ -6024,10 +6024,10 @@
         <v>0</v>
       </c>
       <c r="J161" s="7">
-        <v>169.9</v>
+        <v>106.6</v>
       </c>
       <c r="K161" s="7">
-        <v>2233.1</v>
+        <v>1402.3</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.35">
@@ -6088,7 +6088,7 @@
         <v>0</v>
       </c>
       <c r="H163" s="7">
-        <v>6725</v>
+        <v>4764.8</v>
       </c>
       <c r="I163" s="7">
         <v>0</v>
@@ -6120,19 +6120,19 @@
         <v>29</v>
       </c>
       <c r="G164" s="7">
-        <v>1926.9</v>
+        <v>1432.2</v>
       </c>
       <c r="H164" s="7">
-        <v>2708.3</v>
+        <v>2000.5</v>
       </c>
       <c r="I164" s="7">
-        <v>64.3</v>
+        <v>48.1</v>
       </c>
       <c r="J164" s="7">
-        <v>77</v>
+        <v>52.2</v>
       </c>
       <c r="K164" s="7">
-        <v>894.6</v>
+        <v>598.29999999999995</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.35">
@@ -6190,19 +6190,19 @@
         <v>13</v>
       </c>
       <c r="G166" s="7">
-        <v>225.7</v>
+        <v>144.30000000000001</v>
       </c>
       <c r="H166" s="7">
-        <v>1427.3</v>
+        <v>944.7</v>
       </c>
       <c r="I166" s="7">
-        <v>1051.9000000000001</v>
+        <v>702.2</v>
       </c>
       <c r="J166" s="7">
-        <v>1065.5</v>
+        <v>708.8</v>
       </c>
       <c r="K166" s="7">
-        <v>842.8</v>
+        <v>565.29999999999995</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.35">
@@ -6225,19 +6225,19 @@
         <v>17</v>
       </c>
       <c r="G167" s="7">
-        <v>2261.8000000000002</v>
+        <v>1468.4</v>
       </c>
       <c r="H167" s="7">
-        <v>1218</v>
+        <v>778.6</v>
       </c>
       <c r="I167" s="7">
-        <v>1515.2</v>
+        <v>969.3</v>
       </c>
       <c r="J167" s="7">
-        <v>680.5</v>
+        <v>440.4</v>
       </c>
       <c r="K167" s="7">
-        <v>842.9</v>
+        <v>536.9</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.35">
@@ -6263,16 +6263,16 @@
         <v>0</v>
       </c>
       <c r="H168" s="7">
-        <v>1001.1</v>
+        <v>681.1</v>
       </c>
       <c r="I168" s="7">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="J168" s="7">
         <v>0</v>
       </c>
       <c r="K168" s="7">
-        <v>54.1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.35">
@@ -6298,16 +6298,16 @@
         <v>0</v>
       </c>
       <c r="H169" s="7">
-        <v>472.2</v>
+        <v>340.9</v>
       </c>
       <c r="I169" s="7">
-        <v>126.1</v>
+        <v>91</v>
       </c>
       <c r="J169" s="7">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="K169" s="7">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.35">
@@ -6330,19 +6330,19 @@
         <v>13</v>
       </c>
       <c r="G170" s="7">
-        <v>4898.3</v>
+        <v>3440.7</v>
       </c>
       <c r="H170" s="7">
-        <v>5539.2</v>
+        <v>3916.9</v>
       </c>
       <c r="I170" s="7">
-        <v>7335.4</v>
+        <v>5002.5</v>
       </c>
       <c r="J170" s="7">
-        <v>6196</v>
+        <v>4305</v>
       </c>
       <c r="K170" s="7">
-        <v>4970.3999999999996</v>
+        <v>3488.7</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.35">
@@ -6365,19 +6365,19 @@
         <v>17</v>
       </c>
       <c r="G171" s="7">
-        <v>2728.4</v>
+        <v>1830.4</v>
       </c>
       <c r="H171" s="7">
-        <v>4024.6</v>
+        <v>2682.6</v>
       </c>
       <c r="I171" s="7">
-        <v>2314.1999999999998</v>
+        <v>1600.7</v>
       </c>
       <c r="J171" s="7">
-        <v>1804</v>
+        <v>1237.0999999999999</v>
       </c>
       <c r="K171" s="7">
-        <v>1872.1</v>
+        <v>1259.2</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.35">
@@ -6409,10 +6409,10 @@
         <v>0</v>
       </c>
       <c r="J172" s="7">
-        <v>411.7</v>
+        <v>257.39999999999998</v>
       </c>
       <c r="K172" s="7">
-        <v>3380.9</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.35">
@@ -6435,7 +6435,7 @@
         <v>33</v>
       </c>
       <c r="G173" s="7">
-        <v>13336.1</v>
+        <v>9366.1</v>
       </c>
       <c r="H173" s="7">
         <v>0</v>
@@ -6470,19 +6470,19 @@
         <v>29</v>
       </c>
       <c r="G174" s="7">
-        <v>2616.6999999999998</v>
+        <v>1953.1</v>
       </c>
       <c r="H174" s="7">
-        <v>1836.6</v>
+        <v>1412.8</v>
       </c>
       <c r="I174" s="7">
-        <v>433</v>
+        <v>333.9</v>
       </c>
       <c r="J174" s="7">
-        <v>997.8</v>
+        <v>707.9</v>
       </c>
       <c r="K174" s="7">
-        <v>1091</v>
+        <v>781.3</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.35">
@@ -6508,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="7">
-        <v>3.1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I175" s="7">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>0</v>
       </c>
       <c r="K175" s="7">
-        <v>9.3000000000000007</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.35">
@@ -6540,19 +6540,19 @@
         <v>13</v>
       </c>
       <c r="G176" s="7">
-        <v>4473.1000000000004</v>
+        <v>3115.5</v>
       </c>
       <c r="H176" s="7">
-        <v>6507.7</v>
+        <v>4418</v>
       </c>
       <c r="I176" s="7">
-        <v>6805.5</v>
+        <v>4624.8999999999996</v>
       </c>
       <c r="J176" s="7">
-        <v>7530.4</v>
+        <v>5400.1</v>
       </c>
       <c r="K176" s="7">
-        <v>5947.4</v>
+        <v>4152.3</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.35">
@@ -6575,19 +6575,19 @@
         <v>17</v>
       </c>
       <c r="G177" s="7">
-        <v>12525.9</v>
+        <v>8211.2999999999993</v>
       </c>
       <c r="H177" s="7">
-        <v>11471.2</v>
+        <v>7428.2</v>
       </c>
       <c r="I177" s="7">
-        <v>16997</v>
+        <v>11031.8</v>
       </c>
       <c r="J177" s="7">
-        <v>11235.3</v>
+        <v>7368.6</v>
       </c>
       <c r="K177" s="7">
-        <v>7253.9</v>
+        <v>4686</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.35">
@@ -6610,10 +6610,10 @@
         <v>18</v>
       </c>
       <c r="G178" s="7">
-        <v>9942.4</v>
+        <v>6973.4</v>
       </c>
       <c r="H178" s="7">
-        <v>3176.9</v>
+        <v>2228.1999999999998</v>
       </c>
       <c r="I178" s="7">
         <v>0</v>
@@ -6622,7 +6622,7 @@
         <v>0</v>
       </c>
       <c r="K178" s="7">
-        <v>164.5</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.35">
@@ -6654,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="7">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K179" s="7">
         <v>0</v>
@@ -6683,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="H180" s="7">
-        <v>4346.7</v>
+        <v>3079.7</v>
       </c>
       <c r="I180" s="7">
         <v>0</v>
@@ -6715,19 +6715,19 @@
         <v>29</v>
       </c>
       <c r="G181" s="7">
-        <v>55.9</v>
+        <v>38.5</v>
       </c>
       <c r="H181" s="7">
-        <v>1491.4</v>
+        <v>1064.8</v>
       </c>
       <c r="I181" s="7">
-        <v>552.1</v>
+        <v>408.5</v>
       </c>
       <c r="J181" s="7">
-        <v>459.6</v>
+        <v>298.10000000000002</v>
       </c>
       <c r="K181" s="7">
-        <v>697.7</v>
+        <v>485.9</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.35">
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H182" s="7">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="I182" s="7">
-        <v>11.6</v>
+        <v>7.5</v>
       </c>
       <c r="J182" s="7">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="K182" s="7">
-        <v>17.600000000000001</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.35">
@@ -6785,19 +6785,19 @@
         <v>13</v>
       </c>
       <c r="G183" s="7">
-        <v>21147.1</v>
+        <v>13830.8</v>
       </c>
       <c r="H183" s="7">
-        <v>42380.3</v>
+        <v>28385.3</v>
       </c>
       <c r="I183" s="7">
-        <v>41792.800000000003</v>
+        <v>27473.9</v>
       </c>
       <c r="J183" s="7">
-        <v>38972</v>
+        <v>26908.3</v>
       </c>
       <c r="K183" s="7">
-        <v>31338.799999999999</v>
+        <v>20930.900000000001</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.35">
@@ -6820,19 +6820,19 @@
         <v>17</v>
       </c>
       <c r="G184" s="7">
-        <v>66748</v>
+        <v>43011.9</v>
       </c>
       <c r="H184" s="7">
-        <v>46913.8</v>
+        <v>29773.4</v>
       </c>
       <c r="I184" s="7">
-        <v>55359.5</v>
+        <v>34984.5</v>
       </c>
       <c r="J184" s="7">
-        <v>46262.6</v>
+        <v>29490.3</v>
       </c>
       <c r="K184" s="7">
-        <v>55376.2</v>
+        <v>35337.4</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.35">
@@ -6855,19 +6855,19 @@
         <v>18</v>
       </c>
       <c r="G185" s="7">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="H185" s="7">
-        <v>6309.7</v>
+        <v>4626.6000000000004</v>
       </c>
       <c r="I185" s="7">
         <v>0</v>
       </c>
       <c r="J185" s="7">
-        <v>981.8</v>
+        <v>614</v>
       </c>
       <c r="K185" s="7">
-        <v>8593.7999999999993</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.35">
@@ -6925,16 +6925,16 @@
         <v>33</v>
       </c>
       <c r="G187" s="7">
-        <v>15862.2</v>
+        <v>11394.4</v>
       </c>
       <c r="H187" s="7">
-        <v>7064.3</v>
+        <v>5009.1000000000004</v>
       </c>
       <c r="I187" s="7">
         <v>0</v>
       </c>
       <c r="J187" s="7">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="K187" s="7">
         <v>0</v>
@@ -6960,19 +6960,19 @@
         <v>29</v>
       </c>
       <c r="G188" s="7">
-        <v>4618</v>
+        <v>3044</v>
       </c>
       <c r="H188" s="7">
-        <v>16142</v>
+        <v>11408.3</v>
       </c>
       <c r="I188" s="7">
-        <v>5599.1</v>
+        <v>4025</v>
       </c>
       <c r="J188" s="7">
-        <v>1087.7</v>
+        <v>698.8</v>
       </c>
       <c r="K188" s="7">
-        <v>7541.6</v>
+        <v>5164.1000000000004</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.35">
@@ -7067,7 +7067,7 @@
         <v>0</v>
       </c>
       <c r="K191" s="10">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.35">
@@ -7096,13 +7096,13 @@
         <v>0</v>
       </c>
       <c r="I192" s="10">
-        <v>1.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J192" s="10">
-        <v>80.099999999999994</v>
+        <v>62.3</v>
       </c>
       <c r="K192" s="10">
-        <v>30</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.35">
@@ -7131,13 +7131,13 @@
         <v>0</v>
       </c>
       <c r="I193" s="10">
-        <v>126.2</v>
+        <v>91.3</v>
       </c>
       <c r="J193" s="10">
-        <v>1179</v>
+        <v>882.1</v>
       </c>
       <c r="K193" s="10">
-        <v>508.8</v>
+        <v>382.1</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.35">
@@ -7172,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="K194" s="10">
-        <v>113.6</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.35">
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="K197" s="10">
-        <v>13.2</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.35">
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="J198" s="10">
-        <v>98.9</v>
+        <v>77</v>
       </c>
       <c r="K198" s="10">
-        <v>477.5</v>
+        <v>360.9</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.35">
@@ -7344,10 +7344,10 @@
         <v>0</v>
       </c>
       <c r="J199" s="10">
-        <v>318.3</v>
+        <v>230.9</v>
       </c>
       <c r="K199" s="10">
-        <v>696.3</v>
+        <v>497</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.35">
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="10">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I206" s="10">
         <v>0</v>
@@ -7615,16 +7615,16 @@
         <v>13</v>
       </c>
       <c r="G207" s="10">
-        <v>51.2</v>
+        <v>47.5</v>
       </c>
       <c r="H207" s="10">
-        <v>24.4</v>
+        <v>22.7</v>
       </c>
       <c r="I207" s="10">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J207" s="10">
-        <v>8.9</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K207" s="10">
         <v>0</v>
@@ -7650,19 +7650,19 @@
         <v>17</v>
       </c>
       <c r="G208" s="10">
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H208" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I208" s="10">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="J208" s="10">
         <v>1</v>
       </c>
       <c r="K208" s="10">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.35">
@@ -7685,16 +7685,16 @@
         <v>29</v>
       </c>
       <c r="G209" s="10">
-        <v>34</v>
+        <v>29.7</v>
       </c>
       <c r="H209" s="10">
-        <v>9</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I209" s="10">
         <v>1</v>
       </c>
       <c r="J209" s="10">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="K209" s="10">
         <v>0</v>
@@ -7755,19 +7755,19 @@
         <v>13</v>
       </c>
       <c r="G211" s="10">
-        <v>17.3</v>
+        <v>15.7</v>
       </c>
       <c r="H211" s="10">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I211" s="10">
         <v>0</v>
       </c>
       <c r="J211" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="K211" s="10">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.35">
@@ -7790,10 +7790,10 @@
         <v>17</v>
       </c>
       <c r="G212" s="10">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H212" s="10">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I212" s="10">
         <v>1</v>
@@ -7942,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="K216" s="10">
-        <v>5.4</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.35">
@@ -7971,13 +7971,13 @@
         <v>0</v>
       </c>
       <c r="I217" s="10">
-        <v>65.599999999999994</v>
+        <v>51</v>
       </c>
       <c r="J217" s="10">
-        <v>45.5</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="K217" s="10">
-        <v>30.4</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.35">
@@ -8006,13 +8006,13 @@
         <v>0</v>
       </c>
       <c r="I218" s="10">
-        <v>1857.7</v>
+        <v>1335.6</v>
       </c>
       <c r="J218" s="10">
-        <v>1769.7</v>
+        <v>1261.8</v>
       </c>
       <c r="K218" s="10">
-        <v>965.9</v>
+        <v>690.3</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.35">
@@ -8073,10 +8073,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="10">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="I220" s="10">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="J220" s="10">
         <v>0</v>
@@ -8105,19 +8105,19 @@
         <v>13</v>
       </c>
       <c r="G221" s="10">
-        <v>99.5</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="H221" s="10">
-        <v>273.3</v>
+        <v>220</v>
       </c>
       <c r="I221" s="10">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="J221" s="10">
-        <v>670.8</v>
+        <v>529.9</v>
       </c>
       <c r="K221" s="10">
-        <v>469.1</v>
+        <v>371.9</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.35">
@@ -8140,19 +8140,19 @@
         <v>17</v>
       </c>
       <c r="G222" s="10">
-        <v>2360.1</v>
+        <v>1715.9</v>
       </c>
       <c r="H222" s="10">
-        <v>1245.4000000000001</v>
+        <v>904.3</v>
       </c>
       <c r="I222" s="10">
-        <v>809.2</v>
+        <v>599.29999999999995</v>
       </c>
       <c r="J222" s="10">
-        <v>335</v>
+        <v>251.4</v>
       </c>
       <c r="K222" s="10">
-        <v>384.3</v>
+        <v>279.2</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.35">
@@ -8175,19 +8175,19 @@
         <v>18</v>
       </c>
       <c r="G223" s="10">
-        <v>500.8</v>
+        <v>381.9</v>
       </c>
       <c r="H223" s="10">
-        <v>46.9</v>
+        <v>37</v>
       </c>
       <c r="I223" s="10">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="J223" s="10">
-        <v>25.9</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="K223" s="10">
-        <v>6.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.35">
@@ -8210,19 +8210,19 @@
         <v>29</v>
       </c>
       <c r="G224" s="10">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="H224" s="10">
-        <v>56.9</v>
+        <v>49.2</v>
       </c>
       <c r="I224" s="10">
-        <v>56.6</v>
+        <v>44.8</v>
       </c>
       <c r="J224" s="10">
-        <v>31.6</v>
+        <v>27.6</v>
       </c>
       <c r="K224" s="10">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.35">
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="K225" s="10">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.35">
@@ -8292,7 +8292,7 @@
         <v>0</v>
       </c>
       <c r="K226" s="10">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.35">
@@ -8321,13 +8321,13 @@
         <v>0</v>
       </c>
       <c r="I227" s="10">
-        <v>36.799999999999997</v>
+        <v>29.9</v>
       </c>
       <c r="J227" s="10">
-        <v>64.599999999999994</v>
+        <v>49.3</v>
       </c>
       <c r="K227" s="10">
-        <v>66.900000000000006</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.35">
@@ -8356,13 +8356,13 @@
         <v>0</v>
       </c>
       <c r="I228" s="10">
-        <v>75.8</v>
+        <v>57.5</v>
       </c>
       <c r="J228" s="10">
-        <v>814.2</v>
+        <v>603.6</v>
       </c>
       <c r="K228" s="10">
-        <v>456.6</v>
+        <v>337.8</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.35">
@@ -8432,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="K230" s="10">
-        <v>36.4</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.35">
@@ -8455,19 +8455,19 @@
         <v>13</v>
       </c>
       <c r="G231" s="10">
-        <v>165.4</v>
+        <v>151.69999999999999</v>
       </c>
       <c r="H231" s="10">
-        <v>139.30000000000001</v>
+        <v>127.7</v>
       </c>
       <c r="I231" s="10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J231" s="10">
-        <v>19.2</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="K231" s="10">
-        <v>18.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.35">
@@ -8490,16 +8490,16 @@
         <v>17</v>
       </c>
       <c r="G232" s="10">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="H232" s="10">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="I232" s="10">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J232" s="10">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K232" s="10">
         <v>0</v>
@@ -8525,19 +8525,19 @@
         <v>29</v>
       </c>
       <c r="G233" s="10">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H233" s="10">
-        <v>25.2</v>
+        <v>21.5</v>
       </c>
       <c r="I233" s="10">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="J233" s="10">
-        <v>100.9</v>
+        <v>87.5</v>
       </c>
       <c r="K233" s="10">
-        <v>100.4</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.35">
@@ -8668,16 +8668,16 @@
         <v>0</v>
       </c>
       <c r="H237" s="10">
-        <v>1631.2</v>
+        <v>1211.5999999999999</v>
       </c>
       <c r="I237" s="10">
-        <v>2314.9</v>
+        <v>1685.7</v>
       </c>
       <c r="J237" s="10">
-        <v>1384.3</v>
+        <v>1024.0999999999999</v>
       </c>
       <c r="K237" s="10">
-        <v>666.9</v>
+        <v>500.4</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.35">
@@ -8703,16 +8703,16 @@
         <v>0</v>
       </c>
       <c r="H238" s="10">
-        <v>163</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="I238" s="10">
-        <v>291.60000000000002</v>
+        <v>229.5</v>
       </c>
       <c r="J238" s="10">
-        <v>539.6</v>
+        <v>397.4</v>
       </c>
       <c r="K238" s="10">
-        <v>296.7</v>
+        <v>211.2</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.35">
@@ -8738,16 +8738,16 @@
         <v>0</v>
       </c>
       <c r="H239" s="10">
-        <v>44.4</v>
+        <v>34.9</v>
       </c>
       <c r="I239" s="10">
-        <v>9.9</v>
+        <v>7.8</v>
       </c>
       <c r="J239" s="10">
-        <v>11.4</v>
+        <v>9</v>
       </c>
       <c r="K239" s="10">
-        <v>73</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.35">
@@ -8805,19 +8805,19 @@
         <v>13</v>
       </c>
       <c r="G241" s="10">
-        <v>33.1</v>
+        <v>28.8</v>
       </c>
       <c r="H241" s="10">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="I241" s="10">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J241" s="10">
-        <v>80.900000000000006</v>
+        <v>61.1</v>
       </c>
       <c r="K241" s="10">
-        <v>43.3</v>
+        <v>35.299999999999997</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.35">
@@ -8840,19 +8840,19 @@
         <v>17</v>
       </c>
       <c r="G242" s="10">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="H242" s="10">
-        <v>328.1</v>
+        <v>249.4</v>
       </c>
       <c r="I242" s="10">
-        <v>438</v>
+        <v>323.89999999999998</v>
       </c>
       <c r="J242" s="10">
-        <v>190.7</v>
+        <v>142.69999999999999</v>
       </c>
       <c r="K242" s="10">
-        <v>143.1</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.35">
@@ -8878,13 +8878,13 @@
         <v>0</v>
       </c>
       <c r="H243" s="10">
-        <v>18</v>
+        <v>15.9</v>
       </c>
       <c r="I243" s="10">
-        <v>13.8</v>
+        <v>12.5</v>
       </c>
       <c r="J243" s="10">
-        <v>14.3</v>
+        <v>12.7</v>
       </c>
       <c r="K243" s="10">
         <v>0</v>
@@ -8910,19 +8910,19 @@
         <v>29</v>
       </c>
       <c r="G244" s="10">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="H244" s="10">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="I244" s="10">
         <v>0</v>
       </c>
       <c r="J244" s="10">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="K244" s="10">
-        <v>34.6</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.35">
@@ -8945,7 +8945,7 @@
         <v>37</v>
       </c>
       <c r="G245" s="10">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H245" s="10">
         <v>0</v>
@@ -8980,19 +8980,19 @@
         <v>13</v>
       </c>
       <c r="G246" s="10">
-        <v>183.1</v>
+        <v>163.9</v>
       </c>
       <c r="H246" s="10">
-        <v>23.9</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="I246" s="10">
-        <v>27.9</v>
+        <v>20.9</v>
       </c>
       <c r="J246" s="10">
-        <v>87.2</v>
+        <v>80</v>
       </c>
       <c r="K246" s="10">
-        <v>53.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.35">
@@ -9015,19 +9015,19 @@
         <v>17</v>
       </c>
       <c r="G247" s="10">
-        <v>169.2</v>
+        <v>132.19999999999999</v>
       </c>
       <c r="H247" s="10">
-        <v>348.2</v>
+        <v>276.5</v>
       </c>
       <c r="I247" s="10">
-        <v>204.8</v>
+        <v>159.6</v>
       </c>
       <c r="J247" s="10">
-        <v>46.4</v>
+        <v>37.6</v>
       </c>
       <c r="K247" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.35">
@@ -9053,13 +9053,13 @@
         <v>0</v>
       </c>
       <c r="H248" s="10">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I248" s="10">
-        <v>1.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J248" s="10">
-        <v>2.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K248" s="10">
         <v>0</v>
@@ -9085,19 +9085,19 @@
         <v>29</v>
       </c>
       <c r="G249" s="10">
-        <v>2.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H249" s="10">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I249" s="10">
         <v>0</v>
       </c>
       <c r="J249" s="10">
-        <v>9.1999999999999993</v>
+        <v>7.6</v>
       </c>
       <c r="K249" s="10">
-        <v>17.8</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.35">
@@ -9123,7 +9123,7 @@
         <v>0</v>
       </c>
       <c r="H250" s="10">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="I250" s="10">
         <v>0</v>
@@ -9155,19 +9155,19 @@
         <v>13</v>
       </c>
       <c r="G251" s="10">
-        <v>159.4</v>
+        <v>120.1</v>
       </c>
       <c r="H251" s="10">
-        <v>407.7</v>
+        <v>305.2</v>
       </c>
       <c r="I251" s="10">
-        <v>502.6</v>
+        <v>367.5</v>
       </c>
       <c r="J251" s="10">
-        <v>2237.1</v>
+        <v>1695.6</v>
       </c>
       <c r="K251" s="10">
-        <v>1725.9</v>
+        <v>1302.9000000000001</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.35">
@@ -9190,19 +9190,19 @@
         <v>17</v>
       </c>
       <c r="G252" s="10">
-        <v>337</v>
+        <v>240.6</v>
       </c>
       <c r="H252" s="10">
-        <v>1526.7</v>
+        <v>1093.2</v>
       </c>
       <c r="I252" s="10">
-        <v>2692</v>
+        <v>1915.4</v>
       </c>
       <c r="J252" s="10">
-        <v>2185.3000000000002</v>
+        <v>1566.5</v>
       </c>
       <c r="K252" s="10">
-        <v>1962.1</v>
+        <v>1398.7</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.35">
@@ -9234,10 +9234,10 @@
         <v>0</v>
       </c>
       <c r="J253" s="10">
-        <v>95.7</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="K253" s="10">
-        <v>255.3</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.35">
@@ -9263,16 +9263,16 @@
         <v>0</v>
       </c>
       <c r="H254" s="10">
-        <v>90.2</v>
+        <v>73</v>
       </c>
       <c r="I254" s="10">
-        <v>53.1</v>
+        <v>43.1</v>
       </c>
       <c r="J254" s="10">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K254" s="10">
-        <v>221.6</v>
+        <v>170.9</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.35">
@@ -9298,7 +9298,7 @@
         <v>0</v>
       </c>
       <c r="H255" s="10">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="I255" s="10">
         <v>0</v>
@@ -9307,7 +9307,7 @@
         <v>0</v>
       </c>
       <c r="K255" s="10">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.35">
@@ -9330,19 +9330,19 @@
         <v>13</v>
       </c>
       <c r="G256" s="10">
-        <v>156.4</v>
+        <v>137</v>
       </c>
       <c r="H256" s="10">
-        <v>159.69999999999999</v>
+        <v>138</v>
       </c>
       <c r="I256" s="10">
-        <v>135.4</v>
+        <v>111.7</v>
       </c>
       <c r="J256" s="10">
-        <v>355.8</v>
+        <v>309.89999999999998</v>
       </c>
       <c r="K256" s="10">
-        <v>753.3</v>
+        <v>597.20000000000005</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.35">
@@ -9365,19 +9365,19 @@
         <v>17</v>
       </c>
       <c r="G257" s="10">
-        <v>1680.9</v>
+        <v>1401.8</v>
       </c>
       <c r="H257" s="10">
-        <v>163.19999999999999</v>
+        <v>136.80000000000001</v>
       </c>
       <c r="I257" s="10">
-        <v>351</v>
+        <v>272.3</v>
       </c>
       <c r="J257" s="10">
-        <v>388.9</v>
+        <v>299.7</v>
       </c>
       <c r="K257" s="10">
-        <v>464.1</v>
+        <v>352.8</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.35">
@@ -9400,19 +9400,19 @@
         <v>18</v>
       </c>
       <c r="G258" s="10">
-        <v>242.7</v>
+        <v>194</v>
       </c>
       <c r="H258" s="10">
-        <v>79</v>
+        <v>64.8</v>
       </c>
       <c r="I258" s="10">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J258" s="10">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="K258" s="10">
-        <v>11.7</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.35">
@@ -9435,19 +9435,19 @@
         <v>29</v>
       </c>
       <c r="G259" s="10">
-        <v>104.6</v>
+        <v>91.4</v>
       </c>
       <c r="H259" s="10">
-        <v>241.9</v>
+        <v>206.6</v>
       </c>
       <c r="I259" s="10">
-        <v>224.3</v>
+        <v>187.9</v>
       </c>
       <c r="J259" s="10">
-        <v>143.9</v>
+        <v>124.1</v>
       </c>
       <c r="K259" s="10">
-        <v>567.20000000000005</v>
+        <v>472.1</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.35">
@@ -9473,7 +9473,7 @@
         <v>0</v>
       </c>
       <c r="H260" s="10">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="I260" s="10">
         <v>0</v>
@@ -9482,7 +9482,7 @@
         <v>0</v>
       </c>
       <c r="K260" s="10">
-        <v>59</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.35">
@@ -9505,19 +9505,19 @@
         <v>13</v>
       </c>
       <c r="G261" s="10">
-        <v>1025.7</v>
+        <v>731.8</v>
       </c>
       <c r="H261" s="10">
-        <v>6804.8</v>
+        <v>5008.6000000000004</v>
       </c>
       <c r="I261" s="10">
-        <v>4645.3</v>
+        <v>3268.9</v>
       </c>
       <c r="J261" s="10">
-        <v>842.5</v>
+        <v>606.9</v>
       </c>
       <c r="K261" s="10">
-        <v>1138.0999999999999</v>
+        <v>829.8</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.35">
@@ -9540,19 +9540,19 @@
         <v>17</v>
       </c>
       <c r="G262" s="10">
-        <v>838.8</v>
+        <v>685.9</v>
       </c>
       <c r="H262" s="10">
-        <v>19.100000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="I262" s="10">
-        <v>36</v>
+        <v>29.6</v>
       </c>
       <c r="J262" s="10">
-        <v>128</v>
+        <v>105.3</v>
       </c>
       <c r="K262" s="10">
-        <v>52.5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.35">
@@ -9610,19 +9610,19 @@
         <v>29</v>
       </c>
       <c r="G264" s="10">
-        <v>3.1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H264" s="10">
-        <v>289.7</v>
+        <v>227.5</v>
       </c>
       <c r="I264" s="10">
-        <v>314.10000000000002</v>
+        <v>243.9</v>
       </c>
       <c r="J264" s="10">
-        <v>1424.5</v>
+        <v>1128.5999999999999</v>
       </c>
       <c r="K264" s="10">
-        <v>1167.5</v>
+        <v>920.5</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.35">
@@ -9657,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="K265" s="10">
-        <v>25.8</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.35">
@@ -9689,10 +9689,10 @@
         <v>0</v>
       </c>
       <c r="J266" s="10">
-        <v>53.8</v>
+        <v>41.9</v>
       </c>
       <c r="K266" s="10">
-        <v>28.6</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.35">
@@ -9724,10 +9724,10 @@
         <v>0</v>
       </c>
       <c r="J267" s="10">
-        <v>40</v>
+        <v>30.8</v>
       </c>
       <c r="K267" s="10">
-        <v>119.6</v>
+        <v>89.4</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.35">
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="K268" s="10">
-        <v>166.6</v>
+        <v>135</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.35">
@@ -9785,13 +9785,13 @@
         <v>37</v>
       </c>
       <c r="G269" s="10">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H269" s="10">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="I269" s="10">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J269" s="10">
         <v>0</v>
@@ -9820,19 +9820,19 @@
         <v>13</v>
       </c>
       <c r="G270" s="10">
-        <v>280.89999999999998</v>
+        <v>210.1</v>
       </c>
       <c r="H270" s="10">
-        <v>732.6</v>
+        <v>592.6</v>
       </c>
       <c r="I270" s="10">
-        <v>1134.5</v>
+        <v>819.5</v>
       </c>
       <c r="J270" s="10">
-        <v>1871.1</v>
+        <v>1615.9</v>
       </c>
       <c r="K270" s="10">
-        <v>1949.5</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.35">
@@ -9855,19 +9855,19 @@
         <v>17</v>
       </c>
       <c r="G271" s="10">
-        <v>7986.8</v>
+        <v>5669</v>
       </c>
       <c r="H271" s="10">
-        <v>3530.1</v>
+        <v>2478.4</v>
       </c>
       <c r="I271" s="10">
-        <v>5059.2</v>
+        <v>3620.5</v>
       </c>
       <c r="J271" s="10">
-        <v>3023</v>
+        <v>2207.4</v>
       </c>
       <c r="K271" s="10">
-        <v>6883.3</v>
+        <v>4984</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.35">
@@ -9890,19 +9890,19 @@
         <v>18</v>
       </c>
       <c r="G272" s="10">
-        <v>217.4</v>
+        <v>161.80000000000001</v>
       </c>
       <c r="H272" s="10">
-        <v>511.6</v>
+        <v>374.4</v>
       </c>
       <c r="I272" s="10">
-        <v>5217.1000000000004</v>
+        <v>3624</v>
       </c>
       <c r="J272" s="10">
-        <v>2261.5</v>
+        <v>1580.9</v>
       </c>
       <c r="K272" s="10">
-        <v>1111.9000000000001</v>
+        <v>779.6</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.35">
@@ -9937,7 +9937,7 @@
         <v>0</v>
       </c>
       <c r="K273" s="10">
-        <v>21.8</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.35">
@@ -9960,19 +9960,19 @@
         <v>29</v>
       </c>
       <c r="G274" s="10">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="H274" s="10">
-        <v>244.6</v>
+        <v>207.3</v>
       </c>
       <c r="I274" s="10">
-        <v>4.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="J274" s="10">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="K274" s="10">
-        <v>479.5</v>
+        <v>395.5</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.35">
@@ -9995,19 +9995,19 @@
         <v>37</v>
       </c>
       <c r="G275" s="10">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H275" s="10">
-        <v>294.39999999999998</v>
+        <v>253.7</v>
       </c>
       <c r="I275" s="10">
-        <v>96.6</v>
+        <v>86.3</v>
       </c>
       <c r="J275" s="10">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K275" s="10">
-        <v>1140.3</v>
+        <v>987.7</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.35">
@@ -10030,19 +10030,19 @@
         <v>13</v>
       </c>
       <c r="G276" s="10">
-        <v>12368.5</v>
+        <v>10240.1</v>
       </c>
       <c r="H276" s="10">
-        <v>12371.3</v>
+        <v>10632.1</v>
       </c>
       <c r="I276" s="10">
-        <v>25164.799999999999</v>
+        <v>19670.3</v>
       </c>
       <c r="J276" s="10">
-        <v>11261.2</v>
+        <v>9490.2000000000007</v>
       </c>
       <c r="K276" s="10">
-        <v>13946.8</v>
+        <v>11679.3</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.35">
@@ -10065,19 +10065,19 @@
         <v>17</v>
       </c>
       <c r="G277" s="10">
-        <v>6239.9</v>
+        <v>4676.7</v>
       </c>
       <c r="H277" s="10">
-        <v>5329.3</v>
+        <v>3929.5</v>
       </c>
       <c r="I277" s="10">
-        <v>6455.8</v>
+        <v>4614.8999999999996</v>
       </c>
       <c r="J277" s="10">
-        <v>6132.4</v>
+        <v>4488.1000000000004</v>
       </c>
       <c r="K277" s="10">
-        <v>4650.3999999999996</v>
+        <v>3406.5</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.35">
@@ -10100,16 +10100,16 @@
         <v>18</v>
       </c>
       <c r="G278" s="10">
-        <v>7213.4</v>
+        <v>6001.4</v>
       </c>
       <c r="H278" s="10">
-        <v>212.3</v>
+        <v>157.5</v>
       </c>
       <c r="I278" s="10">
-        <v>32.9</v>
+        <v>26.6</v>
       </c>
       <c r="J278" s="10">
-        <v>59.5</v>
+        <v>44.3</v>
       </c>
       <c r="K278" s="10">
         <v>0</v>
@@ -10138,7 +10138,7 @@
         <v>0</v>
       </c>
       <c r="H279" s="10">
-        <v>4716.7</v>
+        <v>4026</v>
       </c>
       <c r="I279" s="10">
         <v>0</v>
@@ -10205,19 +10205,19 @@
         <v>29</v>
       </c>
       <c r="G281" s="10">
-        <v>5087.8</v>
+        <v>4334.7</v>
       </c>
       <c r="H281" s="10">
-        <v>6773.6</v>
+        <v>5854.1</v>
       </c>
       <c r="I281" s="10">
-        <v>3359.6</v>
+        <v>2938.2</v>
       </c>
       <c r="J281" s="10">
-        <v>11164</v>
+        <v>9665.2999999999993</v>
       </c>
       <c r="K281" s="10">
-        <v>23133</v>
+        <v>20067.5</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.35">
@@ -10278,16 +10278,16 @@
         <v>0</v>
       </c>
       <c r="H283" s="10">
-        <v>1718.2</v>
+        <v>1474.3</v>
       </c>
       <c r="I283" s="10">
-        <v>35.4</v>
+        <v>30.1</v>
       </c>
       <c r="J283" s="10">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="K283" s="10">
-        <v>305.3</v>
+        <v>256.2</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.35">
@@ -10310,19 +10310,19 @@
         <v>13</v>
       </c>
       <c r="G284" s="10">
-        <v>5923.5</v>
+        <v>4641.3</v>
       </c>
       <c r="H284" s="10">
-        <v>5853</v>
+        <v>4476.8999999999996</v>
       </c>
       <c r="I284" s="10">
-        <v>6325.5</v>
+        <v>4792.3999999999996</v>
       </c>
       <c r="J284" s="10">
-        <v>4464.6000000000004</v>
+        <v>3507.5</v>
       </c>
       <c r="K284" s="10">
-        <v>6656.6</v>
+        <v>5125.6000000000004</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.35">
@@ -10345,19 +10345,19 @@
         <v>17</v>
       </c>
       <c r="G285" s="10">
-        <v>10136.299999999999</v>
+        <v>7935.8</v>
       </c>
       <c r="H285" s="10">
-        <v>2990.7</v>
+        <v>2175.3000000000002</v>
       </c>
       <c r="I285" s="10">
-        <v>3374.9</v>
+        <v>2415.5</v>
       </c>
       <c r="J285" s="10">
-        <v>4710.6000000000004</v>
+        <v>3475</v>
       </c>
       <c r="K285" s="10">
-        <v>2746.3</v>
+        <v>1977.2</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.35">
@@ -10380,19 +10380,19 @@
         <v>18</v>
       </c>
       <c r="G286" s="10">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H286" s="10">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="I286" s="10">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J286" s="10">
         <v>0</v>
       </c>
       <c r="K286" s="10">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.35">
@@ -10485,19 +10485,19 @@
         <v>29</v>
       </c>
       <c r="G289" s="10">
-        <v>137.1</v>
+        <v>127.8</v>
       </c>
       <c r="H289" s="10">
-        <v>9896.7999999999993</v>
+        <v>8305.4</v>
       </c>
       <c r="I289" s="10">
-        <v>5228</v>
+        <v>4359.2</v>
       </c>
       <c r="J289" s="10">
-        <v>6358.4</v>
+        <v>5223.6000000000004</v>
       </c>
       <c r="K289" s="10">
-        <v>11672.1</v>
+        <v>9523.5</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.35">
@@ -10701,13 +10701,13 @@
         <v>0</v>
       </c>
       <c r="I295" s="10">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J295" s="10">
-        <v>570.20000000000005</v>
+        <v>421.9</v>
       </c>
       <c r="K295" s="10">
-        <v>396.1</v>
+        <v>289</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.35">
@@ -10736,13 +10736,13 @@
         <v>0</v>
       </c>
       <c r="I296" s="10">
-        <v>2.7</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J296" s="10">
-        <v>29.4</v>
+        <v>23.5</v>
       </c>
       <c r="K296" s="10">
-        <v>184.8</v>
+        <v>144.6</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.35">
@@ -10777,7 +10777,7 @@
         <v>0</v>
       </c>
       <c r="K297" s="10">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.35">
@@ -10806,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="I298" s="10">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J298" s="10">
         <v>0</v>
@@ -10835,19 +10835,19 @@
         <v>13</v>
       </c>
       <c r="G299" s="10">
-        <v>50.8</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="H299" s="10">
-        <v>435.9</v>
+        <v>361.6</v>
       </c>
       <c r="I299" s="10">
-        <v>534.79999999999995</v>
+        <v>406.7</v>
       </c>
       <c r="J299" s="10">
-        <v>1448.2</v>
+        <v>1082.4000000000001</v>
       </c>
       <c r="K299" s="10">
-        <v>1196.5999999999999</v>
+        <v>897.8</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.35">
@@ -10870,19 +10870,19 @@
         <v>17</v>
       </c>
       <c r="G300" s="10">
-        <v>3144</v>
+        <v>2239.8000000000002</v>
       </c>
       <c r="H300" s="10">
-        <v>3690.4</v>
+        <v>2669</v>
       </c>
       <c r="I300" s="10">
-        <v>2849.2</v>
+        <v>2005.8</v>
       </c>
       <c r="J300" s="10">
-        <v>633.29999999999995</v>
+        <v>463.7</v>
       </c>
       <c r="K300" s="10">
-        <v>191.1</v>
+        <v>137.9</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.35">
@@ -10905,16 +10905,16 @@
         <v>18</v>
       </c>
       <c r="G301" s="10">
-        <v>1569.3</v>
+        <v>1113.4000000000001</v>
       </c>
       <c r="H301" s="10">
-        <v>237.6</v>
+        <v>172.7</v>
       </c>
       <c r="I301" s="10">
-        <v>88.3</v>
+        <v>63.3</v>
       </c>
       <c r="J301" s="10">
-        <v>41.8</v>
+        <v>31.3</v>
       </c>
       <c r="K301" s="10">
         <v>0</v>
@@ -10943,16 +10943,16 @@
         <v>0</v>
       </c>
       <c r="H302" s="10">
-        <v>34.4</v>
+        <v>29.1</v>
       </c>
       <c r="I302" s="10">
-        <v>42.3</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="J302" s="10">
-        <v>13.3</v>
+        <v>11</v>
       </c>
       <c r="K302" s="10">
-        <v>482.7</v>
+        <v>386.5</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.35">
@@ -11013,10 +11013,10 @@
         <v>0</v>
       </c>
       <c r="H304" s="10">
-        <v>52.7</v>
+        <v>48</v>
       </c>
       <c r="I304" s="10">
-        <v>13</v>
+        <v>11.6</v>
       </c>
       <c r="J304" s="10">
         <v>0</v>
@@ -11045,19 +11045,19 @@
         <v>13</v>
       </c>
       <c r="G305" s="10">
-        <v>26.9</v>
+        <v>21.3</v>
       </c>
       <c r="H305" s="10">
-        <v>127</v>
+        <v>95.8</v>
       </c>
       <c r="I305" s="10">
-        <v>161.4</v>
+        <v>120.7</v>
       </c>
       <c r="J305" s="10">
-        <v>558.20000000000005</v>
+        <v>416.3</v>
       </c>
       <c r="K305" s="10">
-        <v>799.8</v>
+        <v>598.70000000000005</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.35">
@@ -11080,19 +11080,19 @@
         <v>17</v>
       </c>
       <c r="G306" s="10">
-        <v>346.7</v>
+        <v>261.2</v>
       </c>
       <c r="H306" s="10">
-        <v>247.7</v>
+        <v>180.6</v>
       </c>
       <c r="I306" s="10">
-        <v>494.6</v>
+        <v>367.3</v>
       </c>
       <c r="J306" s="10">
-        <v>1014.9</v>
+        <v>741.4</v>
       </c>
       <c r="K306" s="10">
-        <v>1382</v>
+        <v>988.7</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.35">
@@ -11115,16 +11115,16 @@
         <v>18</v>
       </c>
       <c r="G307" s="10">
-        <v>780.9</v>
+        <v>598.1</v>
       </c>
       <c r="H307" s="10">
-        <v>365.4</v>
+        <v>263.10000000000002</v>
       </c>
       <c r="I307" s="10">
-        <v>360.5</v>
+        <v>256.7</v>
       </c>
       <c r="J307" s="10">
-        <v>149.30000000000001</v>
+        <v>108.7</v>
       </c>
       <c r="K307" s="10">
         <v>0</v>
@@ -11153,16 +11153,16 @@
         <v>0</v>
       </c>
       <c r="H308" s="10">
-        <v>1287.3</v>
+        <v>1041.2</v>
       </c>
       <c r="I308" s="10">
-        <v>161.4</v>
+        <v>129.19999999999999</v>
       </c>
       <c r="J308" s="10">
-        <v>16.2</v>
+        <v>13.9</v>
       </c>
       <c r="K308" s="10">
-        <v>286.7</v>
+        <v>229.5</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.35">
@@ -11188,7 +11188,7 @@
         <v>0</v>
       </c>
       <c r="H309" s="10">
-        <v>148.30000000000001</v>
+        <v>128.30000000000001</v>
       </c>
       <c r="I309" s="10">
         <v>0</v>
@@ -11220,19 +11220,19 @@
         <v>13</v>
       </c>
       <c r="G310" s="10">
-        <v>871.5</v>
+        <v>643</v>
       </c>
       <c r="H310" s="10">
-        <v>2155.9</v>
+        <v>1612.5</v>
       </c>
       <c r="I310" s="10">
-        <v>2308.8000000000002</v>
+        <v>1696.7</v>
       </c>
       <c r="J310" s="10">
-        <v>2542.9</v>
+        <v>1888.9</v>
       </c>
       <c r="K310" s="10">
-        <v>2850.8</v>
+        <v>2108.3000000000002</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.35">
@@ -11255,19 +11255,19 @@
         <v>17</v>
       </c>
       <c r="G311" s="10">
-        <v>870</v>
+        <v>704.9</v>
       </c>
       <c r="H311" s="10">
-        <v>68.8</v>
+        <v>54.1</v>
       </c>
       <c r="I311" s="10">
-        <v>627.20000000000005</v>
+        <v>431.5</v>
       </c>
       <c r="J311" s="10">
-        <v>1674</v>
+        <v>1194.3</v>
       </c>
       <c r="K311" s="10">
-        <v>3617.6</v>
+        <v>2568.4</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.35">
@@ -11302,7 +11302,7 @@
         <v>0</v>
       </c>
       <c r="K312" s="10">
-        <v>6.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.35">
@@ -11325,19 +11325,19 @@
         <v>29</v>
       </c>
       <c r="G313" s="10">
-        <v>88.2</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="H313" s="10">
-        <v>1354.2</v>
+        <v>1081.9000000000001</v>
       </c>
       <c r="I313" s="10">
-        <v>137.69999999999999</v>
+        <v>113.1</v>
       </c>
       <c r="J313" s="10">
-        <v>344.3</v>
+        <v>272.5</v>
       </c>
       <c r="K313" s="10">
-        <v>38.4</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.35">
@@ -11398,16 +11398,16 @@
         <v>0</v>
       </c>
       <c r="H315" s="10">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I315" s="10">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J315" s="10">
         <v>0</v>
       </c>
       <c r="K315" s="10">
-        <v>26.5</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.35">
@@ -11430,19 +11430,19 @@
         <v>13</v>
       </c>
       <c r="G316" s="10">
-        <v>231.6</v>
+        <v>207.1</v>
       </c>
       <c r="H316" s="10">
-        <v>120.5</v>
+        <v>107.4</v>
       </c>
       <c r="I316" s="10">
-        <v>91</v>
+        <v>84.6</v>
       </c>
       <c r="J316" s="10">
-        <v>20.6</v>
+        <v>19.5</v>
       </c>
       <c r="K316" s="10">
-        <v>50.1</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.35">
@@ -11465,16 +11465,16 @@
         <v>17</v>
       </c>
       <c r="G317" s="10">
-        <v>62.3</v>
+        <v>52.9</v>
       </c>
       <c r="H317" s="10">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="I317" s="10">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J317" s="10">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K317" s="10">
         <v>0</v>
@@ -11500,19 +11500,19 @@
         <v>29</v>
       </c>
       <c r="G318" s="10">
-        <v>148.69999999999999</v>
+        <v>140.4</v>
       </c>
       <c r="H318" s="10">
-        <v>110.6</v>
+        <v>105.9</v>
       </c>
       <c r="I318" s="10">
-        <v>18.7</v>
+        <v>17.5</v>
       </c>
       <c r="J318" s="10">
-        <v>113.6</v>
+        <v>106.1</v>
       </c>
       <c r="K318" s="10">
-        <v>217.8</v>
+        <v>203.1</v>
       </c>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.35">
@@ -11538,10 +11538,10 @@
         <v>0</v>
       </c>
       <c r="H319" s="10">
-        <v>80.400000000000006</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="I319" s="10">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J319" s="10">
         <v>0</v>
@@ -11570,19 +11570,19 @@
         <v>13</v>
       </c>
       <c r="G320" s="10">
-        <v>645</v>
+        <v>472.1</v>
       </c>
       <c r="H320" s="10">
-        <v>1343.7</v>
+        <v>976.1</v>
       </c>
       <c r="I320" s="10">
-        <v>4091.5</v>
+        <v>2894.3</v>
       </c>
       <c r="J320" s="10">
-        <v>2150.1</v>
+        <v>1561.9</v>
       </c>
       <c r="K320" s="10">
-        <v>1544.7</v>
+        <v>1138.9000000000001</v>
       </c>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.35">
@@ -11605,19 +11605,19 @@
         <v>17</v>
       </c>
       <c r="G321" s="10">
-        <v>829.6</v>
+        <v>688.2</v>
       </c>
       <c r="H321" s="10">
-        <v>27.5</v>
+        <v>22.2</v>
       </c>
       <c r="I321" s="10">
-        <v>42.3</v>
+        <v>32.9</v>
       </c>
       <c r="J321" s="10">
-        <v>217.3</v>
+        <v>171</v>
       </c>
       <c r="K321" s="10">
-        <v>76</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.35">
@@ -11640,19 +11640,19 @@
         <v>29</v>
       </c>
       <c r="G322" s="10">
-        <v>6.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H322" s="10">
-        <v>1344.4</v>
+        <v>1098.2</v>
       </c>
       <c r="I322" s="10">
-        <v>92.5</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="J322" s="10">
-        <v>53.3</v>
+        <v>42.5</v>
       </c>
       <c r="K322" s="10">
-        <v>506.3</v>
+        <v>391.3</v>
       </c>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.35">
@@ -11681,7 +11681,7 @@
         <v>5</v>
       </c>
       <c r="I323" s="10">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="J323" s="10">
         <v>0</v>
@@ -11710,19 +11710,19 @@
         <v>13</v>
       </c>
       <c r="G324" s="10">
-        <v>105.8</v>
+        <v>88.9</v>
       </c>
       <c r="H324" s="10">
-        <v>261</v>
+        <v>208.6</v>
       </c>
       <c r="I324" s="10">
-        <v>273.3</v>
+        <v>215.7</v>
       </c>
       <c r="J324" s="10">
-        <v>284.7</v>
+        <v>224</v>
       </c>
       <c r="K324" s="10">
-        <v>276.8</v>
+        <v>219.5</v>
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.35">
@@ -11745,19 +11745,19 @@
         <v>17</v>
       </c>
       <c r="G325" s="10">
-        <v>1634.4</v>
+        <v>1322.3</v>
       </c>
       <c r="H325" s="10">
-        <v>344.7</v>
+        <v>266.2</v>
       </c>
       <c r="I325" s="10">
-        <v>232.9</v>
+        <v>186.9</v>
       </c>
       <c r="J325" s="10">
-        <v>107.6</v>
+        <v>86.6</v>
       </c>
       <c r="K325" s="10">
-        <v>47.4</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.35">
@@ -11783,16 +11783,16 @@
         <v>0</v>
       </c>
       <c r="H326" s="10">
-        <v>314.3</v>
+        <v>258.10000000000002</v>
       </c>
       <c r="I326" s="10">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="J326" s="10">
-        <v>229.6</v>
+        <v>190.2</v>
       </c>
       <c r="K326" s="10">
-        <v>279.89999999999998</v>
+        <v>223.3</v>
       </c>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.35">
@@ -11885,7 +11885,7 @@
         <v>29</v>
       </c>
       <c r="G329" s="10">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H329" s="10">
         <v>0</v>
@@ -11926,13 +11926,13 @@
         <v>0</v>
       </c>
       <c r="I330" s="10">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J330" s="10">
         <v>0</v>
       </c>
       <c r="K330" s="10">
-        <v>32.700000000000003</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.35">
@@ -11955,19 +11955,19 @@
         <v>13</v>
       </c>
       <c r="G331" s="10">
-        <v>336.2</v>
+        <v>258.10000000000002</v>
       </c>
       <c r="H331" s="10">
-        <v>828.8</v>
+        <v>720.5</v>
       </c>
       <c r="I331" s="10">
-        <v>668.4</v>
+        <v>527.1</v>
       </c>
       <c r="J331" s="10">
-        <v>1597.8</v>
+        <v>1330.1</v>
       </c>
       <c r="K331" s="10">
-        <v>3264.3</v>
+        <v>2617.1</v>
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.35">
@@ -11990,19 +11990,19 @@
         <v>17</v>
       </c>
       <c r="G332" s="10">
-        <v>5764.9</v>
+        <v>4261.3</v>
       </c>
       <c r="H332" s="10">
-        <v>4640.6000000000004</v>
+        <v>3423.5</v>
       </c>
       <c r="I332" s="10">
-        <v>2841.6</v>
+        <v>2091.5</v>
       </c>
       <c r="J332" s="10">
-        <v>923.9</v>
+        <v>695.1</v>
       </c>
       <c r="K332" s="10">
-        <v>512.6</v>
+        <v>369</v>
       </c>
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.35">
@@ -12025,10 +12025,10 @@
         <v>18</v>
       </c>
       <c r="G333" s="10">
-        <v>521.29999999999995</v>
+        <v>431.8</v>
       </c>
       <c r="H333" s="10">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="I333" s="10">
         <v>0</v>
@@ -12037,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="K333" s="10">
-        <v>7.8</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.35">
@@ -12060,19 +12060,19 @@
         <v>29</v>
       </c>
       <c r="G334" s="10">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="H334" s="10">
-        <v>796.6</v>
+        <v>741.6</v>
       </c>
       <c r="I334" s="10">
-        <v>121.5</v>
+        <v>113.3</v>
       </c>
       <c r="J334" s="10">
-        <v>101.8</v>
+        <v>87.8</v>
       </c>
       <c r="K334" s="10">
-        <v>3370.4</v>
+        <v>2750.8</v>
       </c>
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.35">
@@ -12095,19 +12095,19 @@
         <v>37</v>
       </c>
       <c r="G335" s="10">
-        <v>2.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H335" s="10">
-        <v>348.4</v>
+        <v>328.3</v>
       </c>
       <c r="I335" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J335" s="10">
         <v>4.3</v>
       </c>
-      <c r="J335" s="10">
-        <v>4.9000000000000004</v>
-      </c>
       <c r="K335" s="10">
-        <v>1850.9</v>
+        <v>1669.6</v>
       </c>
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.35">
@@ -12130,19 +12130,19 @@
         <v>13</v>
       </c>
       <c r="G336" s="10">
-        <v>22767</v>
+        <v>19593.8</v>
       </c>
       <c r="H336" s="10">
-        <v>14378.4</v>
+        <v>12449.9</v>
       </c>
       <c r="I336" s="10">
-        <v>15626.7</v>
+        <v>12743.5</v>
       </c>
       <c r="J336" s="10">
-        <v>7456.1</v>
+        <v>6034.5</v>
       </c>
       <c r="K336" s="10">
-        <v>4574.3999999999996</v>
+        <v>3681.3</v>
       </c>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.35">
@@ -12165,19 +12165,19 @@
         <v>17</v>
       </c>
       <c r="G337" s="10">
-        <v>4804.8999999999996</v>
+        <v>3726.5</v>
       </c>
       <c r="H337" s="10">
-        <v>1769.5</v>
+        <v>1333.4</v>
       </c>
       <c r="I337" s="10">
-        <v>2841.8</v>
+        <v>2040.5</v>
       </c>
       <c r="J337" s="10">
-        <v>3011.1</v>
+        <v>2177.6999999999998</v>
       </c>
       <c r="K337" s="10">
-        <v>1847.7</v>
+        <v>1334.9</v>
       </c>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.35">
@@ -12238,13 +12238,13 @@
         <v>0</v>
       </c>
       <c r="H339" s="10">
-        <v>1791.1</v>
+        <v>1528.9</v>
       </c>
       <c r="I339" s="10">
-        <v>3515.1</v>
+        <v>2921.9</v>
       </c>
       <c r="J339" s="10">
-        <v>98.4</v>
+        <v>85.4</v>
       </c>
       <c r="K339" s="10">
         <v>0</v>
@@ -12270,19 +12270,19 @@
         <v>29</v>
       </c>
       <c r="G340" s="10">
-        <v>6994.2</v>
+        <v>6200.4</v>
       </c>
       <c r="H340" s="10">
-        <v>8407.7000000000007</v>
+        <v>7822.6</v>
       </c>
       <c r="I340" s="10">
-        <v>3246.1</v>
+        <v>3042.7</v>
       </c>
       <c r="J340" s="10">
-        <v>16857.3</v>
+        <v>14284.8</v>
       </c>
       <c r="K340" s="10">
-        <v>20401.400000000001</v>
+        <v>17361.8</v>
       </c>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.35">
@@ -12317,7 +12317,7 @@
         <v>0</v>
       </c>
       <c r="K341" s="10">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.35">
@@ -12340,7 +12340,7 @@
         <v>13</v>
       </c>
       <c r="G342" s="10">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="H342" s="10">
         <v>0</v>
@@ -12375,19 +12375,19 @@
         <v>29</v>
       </c>
       <c r="G343" s="10">
-        <v>45.4</v>
+        <v>43.7</v>
       </c>
       <c r="H343" s="10">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="I343" s="10">
-        <v>10.8</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J343" s="10">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="K343" s="10">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.35">
@@ -12410,19 +12410,19 @@
         <v>37</v>
       </c>
       <c r="G344" s="10">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="H344" s="10">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="I344" s="10">
-        <v>17.7</v>
+        <v>15.8</v>
       </c>
       <c r="J344" s="10">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="K344" s="10">
-        <v>330.6</v>
+        <v>282</v>
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.35">
@@ -12445,19 +12445,19 @@
         <v>13</v>
       </c>
       <c r="G345" s="10">
-        <v>9744.6</v>
+        <v>8083.9</v>
       </c>
       <c r="H345" s="10">
-        <v>21481.9</v>
+        <v>17678.8</v>
       </c>
       <c r="I345" s="10">
-        <v>32720.7</v>
+        <v>25917.4</v>
       </c>
       <c r="J345" s="10">
-        <v>26883.599999999999</v>
+        <v>22520.2</v>
       </c>
       <c r="K345" s="10">
-        <v>19881.900000000001</v>
+        <v>16591.8</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.35">
@@ -12480,19 +12480,19 @@
         <v>17</v>
       </c>
       <c r="G346" s="10">
-        <v>21576.9</v>
+        <v>16277.2</v>
       </c>
       <c r="H346" s="10">
-        <v>9459.5</v>
+        <v>6744.4</v>
       </c>
       <c r="I346" s="10">
-        <v>4372.3999999999996</v>
+        <v>3168.1</v>
       </c>
       <c r="J346" s="10">
-        <v>7163.8</v>
+        <v>5413.6</v>
       </c>
       <c r="K346" s="10">
-        <v>3233.9</v>
+        <v>2331.9</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.35">
@@ -12550,19 +12550,19 @@
         <v>29</v>
       </c>
       <c r="G348" s="10">
-        <v>1243.9000000000001</v>
+        <v>1032.8</v>
       </c>
       <c r="H348" s="10">
-        <v>7106</v>
+        <v>5855.3</v>
       </c>
       <c r="I348" s="10">
-        <v>6421.9</v>
+        <v>5307.3</v>
       </c>
       <c r="J348" s="10">
-        <v>2363.5</v>
+        <v>1996.8</v>
       </c>
       <c r="K348" s="10">
-        <v>10796.2</v>
+        <v>8705.6</v>
       </c>
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.35">
@@ -12585,19 +12585,19 @@
         <v>37</v>
       </c>
       <c r="G349" s="10">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H349" s="10">
-        <v>53.6</v>
+        <v>50.3</v>
       </c>
       <c r="I349" s="10">
-        <v>46.7</v>
+        <v>42.7</v>
       </c>
       <c r="J349" s="10">
         <v>0</v>
       </c>
       <c r="K349" s="10">
-        <v>14.2</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.35">
@@ -12620,19 +12620,19 @@
         <v>13</v>
       </c>
       <c r="G350" s="10">
-        <v>1343.9</v>
+        <v>1061.2</v>
       </c>
       <c r="H350" s="10">
-        <v>2444.1999999999998</v>
+        <v>1790</v>
       </c>
       <c r="I350" s="10">
-        <v>1664.5</v>
+        <v>1214.2</v>
       </c>
       <c r="J350" s="10">
-        <v>1123.9000000000001</v>
+        <v>837.7</v>
       </c>
       <c r="K350" s="10">
-        <v>446.2</v>
+        <v>332</v>
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.35">
@@ -12655,19 +12655,19 @@
         <v>17</v>
       </c>
       <c r="G351" s="10">
-        <v>1303.4000000000001</v>
+        <v>1030.3</v>
       </c>
       <c r="H351" s="10">
-        <v>843.1</v>
+        <v>653.1</v>
       </c>
       <c r="I351" s="10">
-        <v>576.70000000000005</v>
+        <v>444.4</v>
       </c>
       <c r="J351" s="10">
-        <v>2054.1</v>
+        <v>1546.7</v>
       </c>
       <c r="K351" s="10">
-        <v>967.4</v>
+        <v>725.5</v>
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.35">
@@ -12690,19 +12690,19 @@
         <v>29</v>
       </c>
       <c r="G352" s="10">
-        <v>49.1</v>
+        <v>37</v>
       </c>
       <c r="H352" s="10">
-        <v>782</v>
+        <v>618.29999999999995</v>
       </c>
       <c r="I352" s="10">
-        <v>529.9</v>
+        <v>421.6</v>
       </c>
       <c r="J352" s="10">
-        <v>1018.9</v>
+        <v>834.7</v>
       </c>
       <c r="K352" s="10">
-        <v>1043.2</v>
+        <v>834.7</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.35">
@@ -12728,16 +12728,16 @@
         <v>0</v>
       </c>
       <c r="H353" s="10">
-        <v>19.7</v>
+        <v>17.8</v>
       </c>
       <c r="I353" s="10">
-        <v>95.2</v>
+        <v>85.8</v>
       </c>
       <c r="J353" s="10">
         <v>0</v>
       </c>
       <c r="K353" s="10">
-        <v>167.8</v>
+        <v>146.69999999999999</v>
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.35">
@@ -12760,19 +12760,19 @@
         <v>13</v>
       </c>
       <c r="G354" s="10">
-        <v>1603.8</v>
+        <v>1178.8</v>
       </c>
       <c r="H354" s="10">
-        <v>1419.8</v>
+        <v>1084</v>
       </c>
       <c r="I354" s="10">
-        <v>728.7</v>
+        <v>545.4</v>
       </c>
       <c r="J354" s="10">
-        <v>383</v>
+        <v>285.2</v>
       </c>
       <c r="K354" s="10">
-        <v>240.9</v>
+        <v>173</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.35">
@@ -12795,19 +12795,19 @@
         <v>17</v>
       </c>
       <c r="G355" s="10">
-        <v>870.5</v>
+        <v>684.5</v>
       </c>
       <c r="H355" s="10">
-        <v>153.4</v>
+        <v>123.4</v>
       </c>
       <c r="I355" s="10">
-        <v>18.600000000000001</v>
+        <v>15.3</v>
       </c>
       <c r="J355" s="10">
-        <v>59.6</v>
+        <v>47.1</v>
       </c>
       <c r="K355" s="10">
-        <v>2.7</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.35">
@@ -12830,19 +12830,19 @@
         <v>29</v>
       </c>
       <c r="G356" s="10">
-        <v>12</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H356" s="10">
-        <v>329.9</v>
+        <v>271.89999999999998</v>
       </c>
       <c r="I356" s="10">
-        <v>352.7</v>
+        <v>282</v>
       </c>
       <c r="J356" s="10">
-        <v>368.8</v>
+        <v>312.3</v>
       </c>
       <c r="K356" s="10">
-        <v>662.5</v>
+        <v>528.9</v>
       </c>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.35">
@@ -12865,19 +12865,19 @@
         <v>37</v>
       </c>
       <c r="G357" s="10">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="H357" s="10">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I357" s="10">
-        <v>10.199999999999999</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J357" s="10">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K357" s="10">
-        <v>2.7</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.35">
@@ -12900,19 +12900,19 @@
         <v>13</v>
       </c>
       <c r="G358" s="10">
-        <v>761</v>
+        <v>589.5</v>
       </c>
       <c r="H358" s="10">
-        <v>1876.3</v>
+        <v>1465.1</v>
       </c>
       <c r="I358" s="10">
-        <v>2129</v>
+        <v>1626.6</v>
       </c>
       <c r="J358" s="10">
-        <v>1720.7</v>
+        <v>1366.6</v>
       </c>
       <c r="K358" s="10">
-        <v>2475.6999999999998</v>
+        <v>1918.2</v>
       </c>
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.35">
@@ -12935,19 +12935,19 @@
         <v>17</v>
       </c>
       <c r="G359" s="10">
-        <v>6423.5</v>
+        <v>4874.1000000000004</v>
       </c>
       <c r="H359" s="10">
-        <v>2624.8</v>
+        <v>1903.5</v>
       </c>
       <c r="I359" s="10">
-        <v>1507.4</v>
+        <v>1096.0999999999999</v>
       </c>
       <c r="J359" s="10">
-        <v>785.2</v>
+        <v>602.20000000000005</v>
       </c>
       <c r="K359" s="10">
-        <v>100.9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.35">
@@ -13110,19 +13110,19 @@
         <v>29</v>
       </c>
       <c r="G364" s="10">
-        <v>213</v>
+        <v>186.1</v>
       </c>
       <c r="H364" s="10">
-        <v>1327</v>
+        <v>1083.2</v>
       </c>
       <c r="I364" s="10">
-        <v>777.3</v>
+        <v>624.70000000000005</v>
       </c>
       <c r="J364" s="10">
-        <v>399.9</v>
+        <v>327.7</v>
       </c>
       <c r="K364" s="10">
-        <v>2204.9</v>
+        <v>1748.6</v>
       </c>
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.35">
@@ -13145,19 +13145,19 @@
         <v>37</v>
       </c>
       <c r="G365" s="10">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H365" s="10">
-        <v>498.9</v>
+        <v>464.3</v>
       </c>
       <c r="I365" s="10">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="J365" s="10">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="K365" s="10">
-        <v>514.79999999999995</v>
+        <v>466.1</v>
       </c>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.35">
@@ -13180,19 +13180,19 @@
         <v>13</v>
       </c>
       <c r="G366" s="10">
-        <v>4988.5</v>
+        <v>4105.8999999999996</v>
       </c>
       <c r="H366" s="10">
-        <v>4713.6000000000004</v>
+        <v>3775</v>
       </c>
       <c r="I366" s="10">
-        <v>4623.7</v>
+        <v>3609.2</v>
       </c>
       <c r="J366" s="10">
-        <v>2979.8</v>
+        <v>2474</v>
       </c>
       <c r="K366" s="10">
-        <v>3911.7</v>
+        <v>3150.1</v>
       </c>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.35">
@@ -13215,19 +13215,19 @@
         <v>17</v>
       </c>
       <c r="G367" s="10">
-        <v>2518</v>
+        <v>1944</v>
       </c>
       <c r="H367" s="10">
-        <v>736.7</v>
+        <v>510.2</v>
       </c>
       <c r="I367" s="10">
-        <v>816.7</v>
+        <v>593</v>
       </c>
       <c r="J367" s="10">
-        <v>2202</v>
+        <v>1618.8</v>
       </c>
       <c r="K367" s="10">
-        <v>684</v>
+        <v>497.6</v>
       </c>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.35">
@@ -13250,13 +13250,13 @@
         <v>18</v>
       </c>
       <c r="G368" s="10">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="H368" s="10">
         <v>0</v>
       </c>
       <c r="I368" s="10">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J368" s="10">
         <v>0</v>
@@ -13285,19 +13285,19 @@
         <v>29</v>
       </c>
       <c r="G369" s="10">
-        <v>1423.2</v>
+        <v>1152.3</v>
       </c>
       <c r="H369" s="10">
-        <v>2337.8000000000002</v>
+        <v>1878</v>
       </c>
       <c r="I369" s="10">
-        <v>1405.5</v>
+        <v>1130.9000000000001</v>
       </c>
       <c r="J369" s="10">
-        <v>4006</v>
+        <v>3196</v>
       </c>
       <c r="K369" s="10">
-        <v>4411.5</v>
+        <v>3495.6</v>
       </c>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.35">
@@ -13323,16 +13323,16 @@
         <v>0</v>
       </c>
       <c r="H370" s="10">
-        <v>11.9</v>
+        <v>10.6</v>
       </c>
       <c r="I370" s="10">
-        <v>24.1</v>
+        <v>21.2</v>
       </c>
       <c r="J370" s="10">
         <v>0</v>
       </c>
       <c r="K370" s="10">
-        <v>486.2</v>
+        <v>402.4</v>
       </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.35">
@@ -13355,19 +13355,19 @@
         <v>13</v>
       </c>
       <c r="G371" s="10">
-        <v>6630.3</v>
+        <v>4925.8</v>
       </c>
       <c r="H371" s="10">
-        <v>4611.1000000000004</v>
+        <v>3418.4</v>
       </c>
       <c r="I371" s="10">
-        <v>8179.9</v>
+        <v>6052.7</v>
       </c>
       <c r="J371" s="10">
-        <v>4939.8</v>
+        <v>3654.5</v>
       </c>
       <c r="K371" s="10">
-        <v>7693.6</v>
+        <v>5689.9</v>
       </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.35">
@@ -13390,19 +13390,19 @@
         <v>17</v>
       </c>
       <c r="G372" s="10">
-        <v>6803.3</v>
+        <v>5135.7</v>
       </c>
       <c r="H372" s="10">
-        <v>3177.3</v>
+        <v>2316.8000000000002</v>
       </c>
       <c r="I372" s="10">
-        <v>2404.8000000000002</v>
+        <v>1702</v>
       </c>
       <c r="J372" s="10">
-        <v>4655.3</v>
+        <v>3420</v>
       </c>
       <c r="K372" s="10">
-        <v>1037.5</v>
+        <v>750.2</v>
       </c>
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.35">
@@ -13428,16 +13428,16 @@
         <v>0</v>
       </c>
       <c r="H373" s="10">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I373" s="10">
-        <v>1.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J373" s="10">
-        <v>23.6</v>
+        <v>18.2</v>
       </c>
       <c r="K373" s="10">
-        <v>8.8000000000000007</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.35">
@@ -13530,19 +13530,19 @@
         <v>29</v>
       </c>
       <c r="G376" s="10">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
       <c r="H376" s="10">
-        <v>7209.5</v>
+        <v>5798.3</v>
       </c>
       <c r="I376" s="10">
-        <v>2451.1999999999998</v>
+        <v>1933.8</v>
       </c>
       <c r="J376" s="10">
-        <v>6141.7</v>
+        <v>4917.3999999999996</v>
       </c>
       <c r="K376" s="10">
-        <v>6264.2</v>
+        <v>5011.2</v>
       </c>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.35">
@@ -13606,13 +13606,13 @@
         <v>0</v>
       </c>
       <c r="I378" s="10">
-        <v>28.3</v>
+        <v>22.4</v>
       </c>
       <c r="J378" s="10">
-        <v>310.8</v>
+        <v>238.7</v>
       </c>
       <c r="K378" s="10">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.35">
@@ -13641,13 +13641,13 @@
         <v>0</v>
       </c>
       <c r="I379" s="10">
-        <v>73.400000000000006</v>
+        <v>58.2</v>
       </c>
       <c r="J379" s="10">
-        <v>829</v>
+        <v>618.5</v>
       </c>
       <c r="K379" s="10">
-        <v>395.4</v>
+        <v>291.7</v>
       </c>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.35">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="K383" s="13">
-        <v>2.6</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.35">
@@ -13812,7 +13812,7 @@
         <v>0</v>
       </c>
       <c r="K384" s="13">
-        <v>5.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.35">
@@ -13911,13 +13911,13 @@
         <v>0</v>
       </c>
       <c r="I387" s="13">
-        <v>1251.7</v>
+        <v>947.6</v>
       </c>
       <c r="J387" s="13">
-        <v>181.3</v>
+        <v>136.69999999999999</v>
       </c>
       <c r="K387" s="13">
-        <v>60</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.35">
@@ -13949,10 +13949,10 @@
         <v>0</v>
       </c>
       <c r="J388" s="13">
-        <v>100.5</v>
+        <v>76.2</v>
       </c>
       <c r="K388" s="13">
-        <v>760.6</v>
+        <v>577.20000000000005</v>
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.35">
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="I389" s="13">
-        <v>5.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J389" s="13">
         <v>0</v>
@@ -14013,16 +14013,16 @@
         <v>0</v>
       </c>
       <c r="H390" s="13">
-        <v>62.3</v>
+        <v>59.1</v>
       </c>
       <c r="I390" s="13">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J390" s="13">
         <v>0</v>
       </c>
       <c r="K390" s="13">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.35">
@@ -14045,19 +14045,19 @@
         <v>13</v>
       </c>
       <c r="G391" s="13">
-        <v>569.20000000000005</v>
+        <v>434.2</v>
       </c>
       <c r="H391" s="13">
-        <v>151.5</v>
+        <v>117.9</v>
       </c>
       <c r="I391" s="13">
-        <v>113.7</v>
+        <v>92.3</v>
       </c>
       <c r="J391" s="13">
-        <v>35.299999999999997</v>
+        <v>28.3</v>
       </c>
       <c r="K391" s="13">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.35">
@@ -14080,19 +14080,19 @@
         <v>29</v>
       </c>
       <c r="G392" s="13">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H392" s="13">
-        <v>54.5</v>
+        <v>46.2</v>
       </c>
       <c r="I392" s="13">
-        <v>5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J392" s="13">
-        <v>161.9</v>
+        <v>143.5</v>
       </c>
       <c r="K392" s="13">
-        <v>71.5</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.35">
@@ -14156,13 +14156,13 @@
         <v>0</v>
       </c>
       <c r="I394" s="13">
-        <v>973.5</v>
+        <v>733.5</v>
       </c>
       <c r="J394" s="13">
-        <v>111.6</v>
+        <v>86.6</v>
       </c>
       <c r="K394" s="13">
-        <v>109.6</v>
+        <v>90.1</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.35">
@@ -14191,13 +14191,13 @@
         <v>0</v>
       </c>
       <c r="I395" s="13">
-        <v>19.2</v>
+        <v>16</v>
       </c>
       <c r="J395" s="13">
-        <v>14.8</v>
+        <v>11.9</v>
       </c>
       <c r="K395" s="13">
-        <v>222.2</v>
+        <v>185.7</v>
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.35">
@@ -14226,7 +14226,7 @@
         <v>0</v>
       </c>
       <c r="I396" s="13">
-        <v>2.8</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J396" s="13">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>0</v>
       </c>
       <c r="K400" s="13">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.35">
@@ -14395,19 +14395,19 @@
         <v>13</v>
       </c>
       <c r="G401" s="13">
-        <v>480.4</v>
+        <v>394.5</v>
       </c>
       <c r="H401" s="13">
-        <v>396.8</v>
+        <v>303.89999999999998</v>
       </c>
       <c r="I401" s="13">
-        <v>220.4</v>
+        <v>169.6</v>
       </c>
       <c r="J401" s="13">
-        <v>93.9</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="K401" s="13">
-        <v>44.9</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.35">
@@ -14430,19 +14430,19 @@
         <v>29</v>
       </c>
       <c r="G402" s="13">
-        <v>2.7</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H402" s="13">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="I402" s="13">
-        <v>25.2</v>
+        <v>20.8</v>
       </c>
       <c r="J402" s="13">
-        <v>107.8</v>
+        <v>88.8</v>
       </c>
       <c r="K402" s="13">
-        <v>54</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.35">
@@ -14500,19 +14500,19 @@
         <v>13</v>
       </c>
       <c r="G404" s="13">
-        <v>1214.2</v>
+        <v>968.3</v>
       </c>
       <c r="H404" s="13">
-        <v>453.8</v>
+        <v>357.2</v>
       </c>
       <c r="I404" s="13">
-        <v>251.1</v>
+        <v>199.9</v>
       </c>
       <c r="J404" s="13">
-        <v>251.2</v>
+        <v>198.1</v>
       </c>
       <c r="K404" s="13">
-        <v>490.1</v>
+        <v>385.9</v>
       </c>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.35">
@@ -14535,19 +14535,19 @@
         <v>29</v>
       </c>
       <c r="G405" s="13">
-        <v>32.200000000000003</v>
+        <v>25.3</v>
       </c>
       <c r="H405" s="13">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="I405" s="13">
-        <v>58.8</v>
+        <v>46</v>
       </c>
       <c r="J405" s="13">
-        <v>138.30000000000001</v>
+        <v>111</v>
       </c>
       <c r="K405" s="13">
-        <v>189</v>
+        <v>148.30000000000001</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.35">
@@ -14827,7 +14827,7 @@
         <v>0</v>
       </c>
       <c r="K413" s="13">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.35">
@@ -14850,19 +14850,19 @@
         <v>13</v>
       </c>
       <c r="G414" s="13">
-        <v>2050.6</v>
+        <v>1545.7</v>
       </c>
       <c r="H414" s="13">
-        <v>1193</v>
+        <v>904.7</v>
       </c>
       <c r="I414" s="13">
-        <v>760.1</v>
+        <v>577.1</v>
       </c>
       <c r="J414" s="13">
-        <v>500.5</v>
+        <v>386.8</v>
       </c>
       <c r="K414" s="13">
-        <v>1386.5</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.35">
@@ -14894,10 +14894,10 @@
         <v>0</v>
       </c>
       <c r="J415" s="13">
-        <v>14.1</v>
+        <v>11.6</v>
       </c>
       <c r="K415" s="13">
-        <v>83.9</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.35">
@@ -14920,19 +14920,19 @@
         <v>29</v>
       </c>
       <c r="G416" s="13">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="H416" s="13">
-        <v>22.5</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="I416" s="13">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="J416" s="13">
-        <v>628.20000000000005</v>
+        <v>517.20000000000005</v>
       </c>
       <c r="K416" s="13">
-        <v>51.8</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.35">
@@ -14967,7 +14967,7 @@
         <v>0</v>
       </c>
       <c r="K417" s="13">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.35">
@@ -15034,10 +15034,10 @@
         <v>0</v>
       </c>
       <c r="J419" s="13">
-        <v>160.69999999999999</v>
+        <v>129.5</v>
       </c>
       <c r="K419" s="13">
-        <v>150.30000000000001</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.35">
@@ -15069,10 +15069,10 @@
         <v>0</v>
       </c>
       <c r="J420" s="13">
-        <v>30.8</v>
+        <v>25.4</v>
       </c>
       <c r="K420" s="13">
-        <v>69.099999999999994</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.35">
@@ -15171,13 +15171,13 @@
         <v>0</v>
       </c>
       <c r="I423" s="13">
-        <v>59</v>
+        <v>46.1</v>
       </c>
       <c r="J423" s="13">
-        <v>230.6</v>
+        <v>179.7</v>
       </c>
       <c r="K423" s="13">
-        <v>121.7</v>
+        <v>93.6</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.35">
@@ -15206,13 +15206,13 @@
         <v>0</v>
       </c>
       <c r="I424" s="13">
-        <v>21.9</v>
+        <v>18.3</v>
       </c>
       <c r="J424" s="13">
-        <v>55.2</v>
+        <v>47.1</v>
       </c>
       <c r="K424" s="13">
-        <v>8.1999999999999993</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.35">
@@ -15247,7 +15247,7 @@
         <v>0</v>
       </c>
       <c r="K425" s="13">
-        <v>7.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.35">
@@ -15375,19 +15375,19 @@
         <v>37</v>
       </c>
       <c r="G429" s="13">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H429" s="13">
-        <v>21.9</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="I429" s="13">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="J429" s="13">
-        <v>463.2</v>
+        <v>384.9</v>
       </c>
       <c r="K429" s="13">
-        <v>125.9</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.35">
@@ -15445,19 +15445,19 @@
         <v>29</v>
       </c>
       <c r="G431" s="13">
-        <v>1468.3</v>
+        <v>1135.5</v>
       </c>
       <c r="H431" s="13">
-        <v>1886.4</v>
+        <v>1436.5</v>
       </c>
       <c r="I431" s="13">
-        <v>1569.3</v>
+        <v>1197.5999999999999</v>
       </c>
       <c r="J431" s="13">
-        <v>1243.8</v>
+        <v>963</v>
       </c>
       <c r="K431" s="13">
-        <v>847.6</v>
+        <v>659.3</v>
       </c>
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.35">
@@ -15521,13 +15521,13 @@
         <v>0</v>
       </c>
       <c r="I433" s="13">
-        <v>77</v>
+        <v>59.7</v>
       </c>
       <c r="J433" s="13">
-        <v>575.20000000000005</v>
+        <v>446.3</v>
       </c>
       <c r="K433" s="13">
-        <v>974.9</v>
+        <v>751.4</v>
       </c>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.35">
@@ -15562,7 +15562,7 @@
         <v>0</v>
       </c>
       <c r="K434" s="13">
-        <v>2.7</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.35">
@@ -15591,13 +15591,13 @@
         <v>0</v>
       </c>
       <c r="I435" s="13">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J435" s="13">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="K435" s="13">
-        <v>19</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.35">
@@ -15661,13 +15661,13 @@
         <v>0</v>
       </c>
       <c r="I437" s="13">
-        <v>196.2</v>
+        <v>151.69999999999999</v>
       </c>
       <c r="J437" s="13">
-        <v>296.60000000000002</v>
+        <v>229.1</v>
       </c>
       <c r="K437" s="13">
-        <v>119.3</v>
+        <v>91.4</v>
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.35">
@@ -15696,13 +15696,13 @@
         <v>0</v>
       </c>
       <c r="I438" s="13">
-        <v>46.3</v>
+        <v>38.1</v>
       </c>
       <c r="J438" s="13">
-        <v>37.9</v>
+        <v>31.8</v>
       </c>
       <c r="K438" s="13">
-        <v>39.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.35">
@@ -15731,13 +15731,13 @@
         <v>0</v>
       </c>
       <c r="I439" s="13">
-        <v>21.5</v>
+        <v>17.5</v>
       </c>
       <c r="J439" s="13">
-        <v>21</v>
+        <v>17.3</v>
       </c>
       <c r="K439" s="13">
-        <v>27.3</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.35">
@@ -15912,7 +15912,7 @@
         <v>0</v>
       </c>
       <c r="K444" s="13">
-        <v>30.9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.35">
@@ -16005,19 +16005,19 @@
         <v>13</v>
       </c>
       <c r="G447" s="13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H447" s="13">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I447" s="13">
         <v>2</v>
       </c>
       <c r="J447" s="13">
-        <v>2.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K447" s="13">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.35">
@@ -16040,16 +16040,16 @@
         <v>17</v>
       </c>
       <c r="G448" s="13">
-        <v>349.9</v>
+        <v>315.5</v>
       </c>
       <c r="H448" s="13">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="I448" s="13">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J448" s="13">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K448" s="13">
         <v>0</v>
@@ -16075,19 +16075,19 @@
         <v>29</v>
       </c>
       <c r="G449" s="13">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="H449" s="13">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I449" s="13">
         <v>0</v>
       </c>
       <c r="J449" s="13">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="K449" s="13">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.35">
@@ -16151,13 +16151,13 @@
         <v>0</v>
       </c>
       <c r="I451" s="13">
-        <v>5893</v>
+        <v>5132.8</v>
       </c>
       <c r="J451" s="13">
-        <v>97.3</v>
+        <v>85.4</v>
       </c>
       <c r="K451" s="13">
-        <v>59.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.35">
@@ -16189,7 +16189,7 @@
         <v>0</v>
       </c>
       <c r="J452" s="13">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="K452" s="13">
         <v>0</v>
@@ -16227,7 +16227,7 @@
         <v>0</v>
       </c>
       <c r="K453" s="13">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.35">
@@ -16262,7 +16262,7 @@
         <v>0</v>
       </c>
       <c r="K454" s="13">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.35">
@@ -16326,7 +16326,7 @@
         <v>0</v>
       </c>
       <c r="I456" s="13">
-        <v>1088.7</v>
+        <v>902.2</v>
       </c>
       <c r="J456" s="13">
         <v>0</v>
@@ -16367,7 +16367,7 @@
         <v>0</v>
       </c>
       <c r="K457" s="13">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.35">
@@ -16390,7 +16390,7 @@
         <v>37</v>
       </c>
       <c r="G458" s="13">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H458" s="13">
         <v>0</v>
@@ -16463,16 +16463,16 @@
         <v>0</v>
       </c>
       <c r="H460" s="13">
-        <v>6963.6</v>
+        <v>6752.5</v>
       </c>
       <c r="I460" s="13">
         <v>0</v>
       </c>
       <c r="J460" s="13">
-        <v>1150.7</v>
+        <v>902</v>
       </c>
       <c r="K460" s="13">
-        <v>9345</v>
+        <v>7499.3</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.35">
@@ -16495,10 +16495,10 @@
         <v>18</v>
       </c>
       <c r="G461" s="13">
-        <v>11415.5</v>
+        <v>10294.6</v>
       </c>
       <c r="H461" s="13">
-        <v>4986.5</v>
+        <v>4407.1000000000004</v>
       </c>
       <c r="I461" s="13">
         <v>0</v>
@@ -16533,7 +16533,7 @@
         <v>0</v>
       </c>
       <c r="H462" s="13">
-        <v>5325.4</v>
+        <v>4800.3</v>
       </c>
       <c r="I462" s="13">
         <v>0</v>
@@ -16565,10 +16565,10 @@
         <v>29</v>
       </c>
       <c r="G463" s="13">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H463" s="13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I463" s="13">
         <v>0</v>
@@ -16641,13 +16641,13 @@
         <v>0</v>
       </c>
       <c r="I465" s="13">
-        <v>2684.5</v>
+        <v>2224.6</v>
       </c>
       <c r="J465" s="13">
-        <v>335.9</v>
+        <v>277.39999999999998</v>
       </c>
       <c r="K465" s="13">
-        <v>2548.4</v>
+        <v>2112.6</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.35">
@@ -16679,10 +16679,10 @@
         <v>0</v>
       </c>
       <c r="J466" s="13">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K466" s="13">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.35">
@@ -16714,7 +16714,7 @@
         <v>0</v>
       </c>
       <c r="J467" s="13">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K467" s="13">
         <v>0</v>
@@ -16749,10 +16749,10 @@
         <v>0</v>
       </c>
       <c r="J468" s="13">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K468" s="13">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.35">
@@ -16778,13 +16778,13 @@
         <v>0</v>
       </c>
       <c r="H469" s="13">
-        <v>20.399999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="I469" s="13">
-        <v>49</v>
+        <v>41.6</v>
       </c>
       <c r="J469" s="13">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K469" s="13">
         <v>0</v>
@@ -16810,19 +16810,19 @@
         <v>13</v>
       </c>
       <c r="G470" s="13">
-        <v>947</v>
+        <v>746.8</v>
       </c>
       <c r="H470" s="13">
-        <v>1968.2</v>
+        <v>1520.2</v>
       </c>
       <c r="I470" s="13">
-        <v>13373.1</v>
+        <v>11040.7</v>
       </c>
       <c r="J470" s="13">
-        <v>1220.4000000000001</v>
+        <v>1004.5</v>
       </c>
       <c r="K470" s="13">
-        <v>12397.4</v>
+        <v>10367.9</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.35">
@@ -16880,19 +16880,19 @@
         <v>29</v>
       </c>
       <c r="G472" s="13">
-        <v>380.7</v>
+        <v>321.10000000000002</v>
       </c>
       <c r="H472" s="13">
-        <v>430.3</v>
+        <v>355</v>
       </c>
       <c r="I472" s="13">
-        <v>471.4</v>
+        <v>380.6</v>
       </c>
       <c r="J472" s="13">
-        <v>1136</v>
+        <v>959.8</v>
       </c>
       <c r="K472" s="13">
-        <v>1200.7</v>
+        <v>995.7</v>
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.35">
@@ -16915,19 +16915,19 @@
         <v>37</v>
       </c>
       <c r="G473" s="13">
-        <v>1806</v>
+        <v>1534.3</v>
       </c>
       <c r="H473" s="13">
-        <v>1608.8</v>
+        <v>1389.6</v>
       </c>
       <c r="I473" s="13">
-        <v>605.6</v>
+        <v>521.4</v>
       </c>
       <c r="J473" s="13">
-        <v>1913.7</v>
+        <v>1640.4</v>
       </c>
       <c r="K473" s="13">
-        <v>2274.6</v>
+        <v>1955.1</v>
       </c>
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.35">
@@ -16950,19 +16950,19 @@
         <v>13</v>
       </c>
       <c r="G474" s="13">
-        <v>315</v>
+        <v>247.9</v>
       </c>
       <c r="H474" s="13">
-        <v>463.6</v>
+        <v>356.1</v>
       </c>
       <c r="I474" s="13">
-        <v>123.8</v>
+        <v>95.6</v>
       </c>
       <c r="J474" s="13">
-        <v>43.8</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="K474" s="13">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.35">
@@ -16988,16 +16988,16 @@
         <v>0</v>
       </c>
       <c r="H475" s="13">
-        <v>570.1</v>
+        <v>517.70000000000005</v>
       </c>
       <c r="I475" s="13">
         <v>0</v>
       </c>
       <c r="J475" s="13">
-        <v>154</v>
+        <v>120.8</v>
       </c>
       <c r="K475" s="13">
-        <v>1526.2</v>
+        <v>1211.3</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.35">
@@ -17020,10 +17020,10 @@
         <v>25</v>
       </c>
       <c r="G476" s="13">
-        <v>6161.7</v>
+        <v>5625.9</v>
       </c>
       <c r="H476" s="13">
-        <v>3307.9</v>
+        <v>2952.5</v>
       </c>
       <c r="I476" s="13">
         <v>0</v>
@@ -17055,19 +17055,19 @@
         <v>29</v>
       </c>
       <c r="G477" s="13">
-        <v>5584.4</v>
+        <v>4891.1000000000004</v>
       </c>
       <c r="H477" s="13">
-        <v>4332.3999999999996</v>
+        <v>3543</v>
       </c>
       <c r="I477" s="13">
-        <v>4142.3999999999996</v>
+        <v>3384.4</v>
       </c>
       <c r="J477" s="13">
-        <v>2153.6999999999998</v>
+        <v>1805.2</v>
       </c>
       <c r="K477" s="13">
-        <v>809.9</v>
+        <v>678.1</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.35">
@@ -17090,13 +17090,13 @@
         <v>37</v>
       </c>
       <c r="G478" s="13">
-        <v>26.9</v>
+        <v>24.5</v>
       </c>
       <c r="H478" s="13">
-        <v>9.6999999999999993</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I478" s="13">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J478" s="13">
         <v>0</v>
@@ -17125,19 +17125,19 @@
         <v>13</v>
       </c>
       <c r="G479" s="13">
-        <v>155.30000000000001</v>
+        <v>119.4</v>
       </c>
       <c r="H479" s="13">
-        <v>65.3</v>
+        <v>52.2</v>
       </c>
       <c r="I479" s="13">
-        <v>1059.5</v>
+        <v>918.1</v>
       </c>
       <c r="J479" s="13">
-        <v>342</v>
+        <v>275.5</v>
       </c>
       <c r="K479" s="13">
-        <v>136.6</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.35">
@@ -17163,16 +17163,16 @@
         <v>0</v>
       </c>
       <c r="H480" s="13">
-        <v>11.8</v>
+        <v>9.4</v>
       </c>
       <c r="I480" s="13">
-        <v>52.8</v>
+        <v>43.7</v>
       </c>
       <c r="J480" s="13">
-        <v>194.1</v>
+        <v>158.9</v>
       </c>
       <c r="K480" s="13">
-        <v>470.2</v>
+        <v>371.5</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.35">
@@ -17195,19 +17195,19 @@
         <v>18</v>
       </c>
       <c r="G481" s="13">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="H481" s="13">
         <v>0</v>
       </c>
       <c r="I481" s="13">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J481" s="13">
         <v>0</v>
       </c>
       <c r="K481" s="13">
-        <v>2.6</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.35">
@@ -17230,19 +17230,19 @@
         <v>29</v>
       </c>
       <c r="G482" s="13">
-        <v>126.6</v>
+        <v>107.1</v>
       </c>
       <c r="H482" s="13">
-        <v>49</v>
+        <v>42.2</v>
       </c>
       <c r="I482" s="13">
-        <v>26.5</v>
+        <v>22.5</v>
       </c>
       <c r="J482" s="13">
         <v>0</v>
       </c>
       <c r="K482" s="13">
-        <v>16.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.35">
@@ -17265,19 +17265,19 @@
         <v>37</v>
       </c>
       <c r="G483" s="13">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H483" s="13">
-        <v>23.9</v>
+        <v>22.7</v>
       </c>
       <c r="I483" s="13">
-        <v>34.6</v>
+        <v>30.5</v>
       </c>
       <c r="J483" s="13">
-        <v>53.1</v>
+        <v>46.2</v>
       </c>
       <c r="K483" s="13">
-        <v>316.5</v>
+        <v>270</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.35">
@@ -17300,19 +17300,19 @@
         <v>13</v>
       </c>
       <c r="G484" s="13">
-        <v>2169.5</v>
+        <v>1679.4</v>
       </c>
       <c r="H484" s="13">
-        <v>1375.8</v>
+        <v>1063</v>
       </c>
       <c r="I484" s="13">
-        <v>1759.4</v>
+        <v>1451.7</v>
       </c>
       <c r="J484" s="13">
-        <v>495.7</v>
+        <v>402.8</v>
       </c>
       <c r="K484" s="13">
-        <v>71.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.35">
@@ -17370,19 +17370,19 @@
         <v>29</v>
       </c>
       <c r="G486" s="13">
-        <v>318.8</v>
+        <v>259.8</v>
       </c>
       <c r="H486" s="13">
-        <v>435.5</v>
+        <v>349.5</v>
       </c>
       <c r="I486" s="13">
-        <v>1625.9</v>
+        <v>1296.4000000000001</v>
       </c>
       <c r="J486" s="13">
-        <v>1615.9</v>
+        <v>1340.6</v>
       </c>
       <c r="K486" s="13">
-        <v>2076.9</v>
+        <v>1668.5</v>
       </c>
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.35">
@@ -17405,19 +17405,19 @@
         <v>37</v>
       </c>
       <c r="G487" s="13">
-        <v>27.7</v>
+        <v>22.3</v>
       </c>
       <c r="H487" s="13">
-        <v>150.69999999999999</v>
+        <v>131.80000000000001</v>
       </c>
       <c r="I487" s="13">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="J487" s="13">
-        <v>102.1</v>
+        <v>84.2</v>
       </c>
       <c r="K487" s="13">
-        <v>312.5</v>
+        <v>260.39999999999998</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.35">
@@ -17440,19 +17440,19 @@
         <v>13</v>
       </c>
       <c r="G488" s="13">
-        <v>949.5</v>
+        <v>781.6</v>
       </c>
       <c r="H488" s="13">
-        <v>342.8</v>
+        <v>267.8</v>
       </c>
       <c r="I488" s="13">
-        <v>398.9</v>
+        <v>315.8</v>
       </c>
       <c r="J488" s="13">
-        <v>448</v>
+        <v>363.6</v>
       </c>
       <c r="K488" s="13">
-        <v>271.3</v>
+        <v>220</v>
       </c>
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.35">
@@ -17475,19 +17475,19 @@
         <v>29</v>
       </c>
       <c r="G489" s="13">
-        <v>1130</v>
+        <v>956.3</v>
       </c>
       <c r="H489" s="13">
-        <v>2400.8000000000002</v>
+        <v>1924.7</v>
       </c>
       <c r="I489" s="13">
-        <v>3562.9</v>
+        <v>2778.1</v>
       </c>
       <c r="J489" s="13">
-        <v>2331.5</v>
+        <v>1927.7</v>
       </c>
       <c r="K489" s="13">
-        <v>1882.2</v>
+        <v>1545.7</v>
       </c>
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.35">
@@ -17837,7 +17837,7 @@
         <v>0</v>
       </c>
       <c r="K499" s="13">
-        <v>54</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="500" spans="1:11" x14ac:dyDescent="0.35">
@@ -17860,7 +17860,7 @@
         <v>25</v>
       </c>
       <c r="G500" s="13">
-        <v>5135.2</v>
+        <v>4633</v>
       </c>
       <c r="H500" s="13">
         <v>0</v>
@@ -17895,7 +17895,7 @@
         <v>29</v>
       </c>
       <c r="G501" s="13">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H501" s="13">
         <v>0</v>
@@ -17933,7 +17933,7 @@
         <v>0</v>
       </c>
       <c r="H502" s="13">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I502" s="13">
         <v>0</v>
@@ -17942,7 +17942,7 @@
         <v>0</v>
       </c>
       <c r="K502" s="13">
-        <v>464.2</v>
+        <v>390.7</v>
       </c>
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.35">
@@ -17971,13 +17971,13 @@
         <v>0</v>
       </c>
       <c r="I503" s="13">
-        <v>704.2</v>
+        <v>528.5</v>
       </c>
       <c r="J503" s="13">
-        <v>764.7</v>
+        <v>578.79999999999995</v>
       </c>
       <c r="K503" s="13">
-        <v>3342.4</v>
+        <v>2482.1999999999998</v>
       </c>
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.35">
@@ -18009,10 +18009,10 @@
         <v>0</v>
       </c>
       <c r="J504" s="13">
-        <v>40.700000000000003</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="K504" s="13">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.35">
@@ -18038,16 +18038,16 @@
         <v>0</v>
       </c>
       <c r="H505" s="13">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="I505" s="13">
-        <v>813.7</v>
+        <v>628.4</v>
       </c>
       <c r="J505" s="13">
-        <v>145.80000000000001</v>
+        <v>112</v>
       </c>
       <c r="K505" s="13">
-        <v>116.2</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.35">
@@ -18073,16 +18073,16 @@
         <v>0</v>
       </c>
       <c r="H506" s="13">
-        <v>486.8</v>
+        <v>462.3</v>
       </c>
       <c r="I506" s="13">
-        <v>246.4</v>
+        <v>229.5</v>
       </c>
       <c r="J506" s="13">
         <v>1</v>
       </c>
       <c r="K506" s="13">
-        <v>697</v>
+        <v>614.4</v>
       </c>
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.35">
@@ -18105,19 +18105,19 @@
         <v>13</v>
       </c>
       <c r="G507" s="13">
-        <v>6210.8</v>
+        <v>4673.3</v>
       </c>
       <c r="H507" s="13">
-        <v>3872.3</v>
+        <v>2877.8</v>
       </c>
       <c r="I507" s="13">
-        <v>4673.7</v>
+        <v>3443.6</v>
       </c>
       <c r="J507" s="13">
-        <v>3032.1</v>
+        <v>2235.5</v>
       </c>
       <c r="K507" s="13">
-        <v>1907.5</v>
+        <v>1458.1</v>
       </c>
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.35">
@@ -18149,10 +18149,10 @@
         <v>0</v>
       </c>
       <c r="J508" s="13">
-        <v>10.4</v>
+        <v>8.9</v>
       </c>
       <c r="K508" s="13">
-        <v>37.6</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="509" spans="1:11" x14ac:dyDescent="0.35">
@@ -18184,10 +18184,10 @@
         <v>0</v>
       </c>
       <c r="J509" s="13">
-        <v>123.2</v>
+        <v>96.6</v>
       </c>
       <c r="K509" s="13">
-        <v>1911.9</v>
+        <v>1517.1</v>
       </c>
     </row>
     <row r="510" spans="1:11" x14ac:dyDescent="0.35">
@@ -18210,19 +18210,19 @@
         <v>29</v>
       </c>
       <c r="G510" s="13">
-        <v>59.1</v>
+        <v>47.3</v>
       </c>
       <c r="H510" s="13">
-        <v>1165.0999999999999</v>
+        <v>948.2</v>
       </c>
       <c r="I510" s="13">
-        <v>1295.7</v>
+        <v>1022.4</v>
       </c>
       <c r="J510" s="13">
-        <v>2490.1</v>
+        <v>2033.6</v>
       </c>
       <c r="K510" s="13">
-        <v>4378</v>
+        <v>3526.6</v>
       </c>
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.35">
@@ -18245,19 +18245,19 @@
         <v>37</v>
       </c>
       <c r="G511" s="13">
-        <v>56</v>
+        <v>51.7</v>
       </c>
       <c r="H511" s="13">
-        <v>8805.2999999999993</v>
+        <v>8088</v>
       </c>
       <c r="I511" s="13">
-        <v>178</v>
+        <v>163.19999999999999</v>
       </c>
       <c r="J511" s="13">
-        <v>41.2</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="K511" s="13">
-        <v>549.70000000000005</v>
+        <v>475.4</v>
       </c>
     </row>
     <row r="512" spans="1:11" x14ac:dyDescent="0.35">
@@ -18280,19 +18280,19 @@
         <v>13</v>
       </c>
       <c r="G512" s="13">
-        <v>16815.599999999999</v>
+        <v>13431.9</v>
       </c>
       <c r="H512" s="13">
-        <v>15306.7</v>
+        <v>12224.2</v>
       </c>
       <c r="I512" s="13">
-        <v>19813.2</v>
+        <v>15807.6</v>
       </c>
       <c r="J512" s="13">
-        <v>13693.5</v>
+        <v>11158.2</v>
       </c>
       <c r="K512" s="13">
-        <v>4910.3</v>
+        <v>4005.7</v>
       </c>
     </row>
     <row r="513" spans="1:11" x14ac:dyDescent="0.35">
@@ -18315,10 +18315,10 @@
         <v>17</v>
       </c>
       <c r="G513" s="13">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="H513" s="13">
-        <v>2382.3000000000002</v>
+        <v>2105.5</v>
       </c>
       <c r="I513" s="13">
         <v>0</v>
@@ -18385,19 +18385,19 @@
         <v>29</v>
       </c>
       <c r="G515" s="13">
-        <v>7534.8</v>
+        <v>6304.1</v>
       </c>
       <c r="H515" s="13">
-        <v>18311</v>
+        <v>15907.2</v>
       </c>
       <c r="I515" s="13">
-        <v>14940.4</v>
+        <v>12696.5</v>
       </c>
       <c r="J515" s="13">
-        <v>20149.8</v>
+        <v>17408.5</v>
       </c>
       <c r="K515" s="13">
-        <v>26019.3</v>
+        <v>21790.6</v>
       </c>
     </row>
     <row r="516" spans="1:11" x14ac:dyDescent="0.35">
@@ -18420,19 +18420,19 @@
         <v>37</v>
       </c>
       <c r="G516" s="13">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="H516" s="13">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="I516" s="13">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="J516" s="13">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K516" s="13">
-        <v>169.6</v>
+        <v>143.4</v>
       </c>
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.35">
@@ -18455,19 +18455,19 @@
         <v>13</v>
       </c>
       <c r="G517" s="13">
-        <v>298.7</v>
+        <v>241.6</v>
       </c>
       <c r="H517" s="13">
-        <v>140.9</v>
+        <v>113.2</v>
       </c>
       <c r="I517" s="13">
-        <v>159.5</v>
+        <v>129.6</v>
       </c>
       <c r="J517" s="13">
-        <v>66</v>
+        <v>52.5</v>
       </c>
       <c r="K517" s="13">
-        <v>10.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.35">
@@ -18490,19 +18490,19 @@
         <v>29</v>
       </c>
       <c r="G518" s="13">
-        <v>347.8</v>
+        <v>289.39999999999998</v>
       </c>
       <c r="H518" s="13">
-        <v>396</v>
+        <v>333.8</v>
       </c>
       <c r="I518" s="13">
-        <v>162.80000000000001</v>
+        <v>137.1</v>
       </c>
       <c r="J518" s="13">
-        <v>262</v>
+        <v>217</v>
       </c>
       <c r="K518" s="13">
-        <v>435.8</v>
+        <v>358.9</v>
       </c>
     </row>
     <row r="519" spans="1:11" x14ac:dyDescent="0.35">
@@ -18528,16 +18528,16 @@
         <v>0</v>
       </c>
       <c r="H519" s="13">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="I519" s="13">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="J519" s="13">
         <v>0</v>
       </c>
       <c r="K519" s="13">
-        <v>8.6999999999999993</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="520" spans="1:11" x14ac:dyDescent="0.35">
@@ -18560,19 +18560,19 @@
         <v>13</v>
       </c>
       <c r="G520" s="13">
-        <v>1796.3</v>
+        <v>1461</v>
       </c>
       <c r="H520" s="13">
-        <v>3248.2</v>
+        <v>2458.3000000000002</v>
       </c>
       <c r="I520" s="13">
-        <v>3051.1</v>
+        <v>2272.4</v>
       </c>
       <c r="J520" s="13">
-        <v>980.6</v>
+        <v>731.3</v>
       </c>
       <c r="K520" s="13">
-        <v>1063.5999999999999</v>
+        <v>824.8</v>
       </c>
     </row>
     <row r="521" spans="1:11" x14ac:dyDescent="0.35">
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="J521" s="13">
-        <v>65.599999999999994</v>
+        <v>47.4</v>
       </c>
       <c r="K521" s="13">
-        <v>123.3</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="522" spans="1:11" x14ac:dyDescent="0.35">
@@ -18665,19 +18665,19 @@
         <v>29</v>
       </c>
       <c r="G523" s="13">
-        <v>80.900000000000006</v>
+        <v>66.2</v>
       </c>
       <c r="H523" s="13">
-        <v>119.6</v>
+        <v>98.3</v>
       </c>
       <c r="I523" s="13">
-        <v>100.2</v>
+        <v>83.4</v>
       </c>
       <c r="J523" s="13">
-        <v>311</v>
+        <v>266.7</v>
       </c>
       <c r="K523" s="13">
-        <v>500.3</v>
+        <v>415.1</v>
       </c>
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.35">
@@ -18703,16 +18703,16 @@
         <v>0</v>
       </c>
       <c r="H524" s="13">
-        <v>279.10000000000002</v>
+        <v>264.89999999999998</v>
       </c>
       <c r="I524" s="13">
-        <v>77.900000000000006</v>
+        <v>67.5</v>
       </c>
       <c r="J524" s="13">
-        <v>76.099999999999994</v>
+        <v>66.8</v>
       </c>
       <c r="K524" s="13">
-        <v>1320.6</v>
+        <v>1201.9000000000001</v>
       </c>
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.35">
@@ -18735,19 +18735,19 @@
         <v>13</v>
       </c>
       <c r="G525" s="13">
-        <v>28129.8</v>
+        <v>20950.5</v>
       </c>
       <c r="H525" s="13">
-        <v>18200.3</v>
+        <v>13664.2</v>
       </c>
       <c r="I525" s="13">
-        <v>21567.8</v>
+        <v>15993.9</v>
       </c>
       <c r="J525" s="13">
-        <v>8640.7999999999993</v>
+        <v>6431.2</v>
       </c>
       <c r="K525" s="13">
-        <v>8126.2</v>
+        <v>6006.3</v>
       </c>
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.35">
@@ -18773,7 +18773,7 @@
         <v>0</v>
       </c>
       <c r="H526" s="13">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I526" s="13">
         <v>0</v>
@@ -18782,7 +18782,7 @@
         <v>0</v>
       </c>
       <c r="K526" s="13">
-        <v>13.5</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.35">
@@ -18840,19 +18840,19 @@
         <v>29</v>
       </c>
       <c r="G528" s="13">
-        <v>1822.5</v>
+        <v>1455</v>
       </c>
       <c r="H528" s="13">
-        <v>2377.6999999999998</v>
+        <v>1914.6</v>
       </c>
       <c r="I528" s="13">
-        <v>1978.6</v>
+        <v>1603.7</v>
       </c>
       <c r="J528" s="13">
-        <v>6942.7</v>
+        <v>5629.5</v>
       </c>
       <c r="K528" s="13">
-        <v>10211.9</v>
+        <v>8185.8</v>
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.35">
@@ -18875,19 +18875,19 @@
         <v>37</v>
       </c>
       <c r="G529" s="13">
-        <v>305.5</v>
+        <v>274.39999999999998</v>
       </c>
       <c r="H529" s="13">
-        <v>2131.4</v>
+        <v>1949.4</v>
       </c>
       <c r="I529" s="13">
-        <v>893.8</v>
+        <v>824.3</v>
       </c>
       <c r="J529" s="13">
-        <v>29.1</v>
+        <v>26</v>
       </c>
       <c r="K529" s="13">
-        <v>1632.5</v>
+        <v>1465.8</v>
       </c>
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.35">
@@ -18910,19 +18910,19 @@
         <v>13</v>
       </c>
       <c r="G530" s="13">
-        <v>26967.9</v>
+        <v>21411.9</v>
       </c>
       <c r="H530" s="13">
-        <v>23902.3</v>
+        <v>19012.599999999999</v>
       </c>
       <c r="I530" s="13">
-        <v>29748.5</v>
+        <v>23672.799999999999</v>
       </c>
       <c r="J530" s="13">
-        <v>15410.8</v>
+        <v>12514.9</v>
       </c>
       <c r="K530" s="13">
-        <v>14456.2</v>
+        <v>11455.3</v>
       </c>
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.35">
@@ -18945,19 +18945,19 @@
         <v>17</v>
       </c>
       <c r="G531" s="13">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="H531" s="13">
-        <v>932.6</v>
+        <v>846.6</v>
       </c>
       <c r="I531" s="13">
-        <v>5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J531" s="13">
         <v>0</v>
       </c>
       <c r="K531" s="13">
-        <v>23.8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.35">
@@ -18983,7 +18983,7 @@
         <v>0</v>
       </c>
       <c r="H532" s="13">
-        <v>1584.1</v>
+        <v>1412.1</v>
       </c>
       <c r="I532" s="13">
         <v>0</v>
@@ -19120,19 +19120,19 @@
         <v>29</v>
       </c>
       <c r="G536" s="13">
-        <v>18231.400000000001</v>
+        <v>15611.7</v>
       </c>
       <c r="H536" s="13">
-        <v>10299.299999999999</v>
+        <v>8772.5</v>
       </c>
       <c r="I536" s="13">
-        <v>7724.9</v>
+        <v>6443.6</v>
       </c>
       <c r="J536" s="13">
-        <v>22443.3</v>
+        <v>19521.2</v>
       </c>
       <c r="K536" s="13">
-        <v>24190.2</v>
+        <v>20523.400000000001</v>
       </c>
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.35">
@@ -19167,7 +19167,7 @@
         <v>0</v>
       </c>
       <c r="K537" s="13">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.35">
@@ -19193,16 +19193,16 @@
         <v>0</v>
       </c>
       <c r="H538" s="13">
-        <v>459.2</v>
+        <v>345.1</v>
       </c>
       <c r="I538" s="13">
-        <v>358.9</v>
+        <v>262.2</v>
       </c>
       <c r="J538" s="13">
-        <v>77.599999999999994</v>
+        <v>58.1</v>
       </c>
       <c r="K538" s="13">
-        <v>516.4</v>
+        <v>381.2</v>
       </c>
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.35">
@@ -19237,7 +19237,7 @@
         <v>0</v>
       </c>
       <c r="K539" s="13">
-        <v>254.6</v>
+        <v>191.4</v>
       </c>
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.35">
@@ -19263,16 +19263,16 @@
         <v>0</v>
       </c>
       <c r="H540" s="13">
-        <v>398.1</v>
+        <v>318</v>
       </c>
       <c r="I540" s="13">
-        <v>633.9</v>
+        <v>487.3</v>
       </c>
       <c r="J540" s="13">
-        <v>644.29999999999995</v>
+        <v>519.1</v>
       </c>
       <c r="K540" s="13">
-        <v>331.5</v>
+        <v>269</v>
       </c>
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.35">
@@ -19330,19 +19330,19 @@
         <v>13</v>
       </c>
       <c r="G542" s="13">
-        <v>134.1</v>
+        <v>120.5</v>
       </c>
       <c r="H542" s="13">
-        <v>139</v>
+        <v>120.5</v>
       </c>
       <c r="I542" s="13">
-        <v>99.9</v>
+        <v>83.3</v>
       </c>
       <c r="J542" s="13">
-        <v>18.7</v>
+        <v>15.8</v>
       </c>
       <c r="K542" s="13">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.35">
@@ -19365,19 +19365,19 @@
         <v>29</v>
       </c>
       <c r="G543" s="13">
-        <v>57.8</v>
+        <v>53</v>
       </c>
       <c r="H543" s="13">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="I543" s="13">
-        <v>34.700000000000003</v>
+        <v>32.4</v>
       </c>
       <c r="J543" s="13">
-        <v>160.1</v>
+        <v>150.19999999999999</v>
       </c>
       <c r="K543" s="13">
-        <v>42.5</v>
+        <v>40.299999999999997</v>
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.35">
@@ -19540,19 +19540,19 @@
         <v>37</v>
       </c>
       <c r="G548" s="13">
-        <v>29.1</v>
+        <v>26</v>
       </c>
       <c r="H548" s="13">
-        <v>52.7</v>
+        <v>51</v>
       </c>
       <c r="I548" s="13">
-        <v>80.400000000000006</v>
+        <v>75.8</v>
       </c>
       <c r="J548" s="13">
-        <v>2908.2</v>
+        <v>2645.6</v>
       </c>
       <c r="K548" s="13">
-        <v>951.2</v>
+        <v>878.4</v>
       </c>
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.35">
@@ -19575,19 +19575,19 @@
         <v>13</v>
       </c>
       <c r="G549" s="13">
-        <v>900.5</v>
+        <v>717.8</v>
       </c>
       <c r="H549" s="13">
-        <v>807.1</v>
+        <v>658</v>
       </c>
       <c r="I549" s="13">
-        <v>1495.8</v>
+        <v>1143.5</v>
       </c>
       <c r="J549" s="13">
-        <v>2509</v>
+        <v>1883.1</v>
       </c>
       <c r="K549" s="13">
-        <v>2409.9</v>
+        <v>1816.7</v>
       </c>
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.35">
@@ -19610,19 +19610,19 @@
         <v>17</v>
       </c>
       <c r="G550" s="13">
-        <v>184.3</v>
+        <v>149.6</v>
       </c>
       <c r="H550" s="13">
-        <v>87.8</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="I550" s="13">
-        <v>20</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="J550" s="13">
-        <v>23.6</v>
+        <v>19.5</v>
       </c>
       <c r="K550" s="13">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.35">
@@ -19645,19 +19645,19 @@
         <v>29</v>
       </c>
       <c r="G551" s="13">
-        <v>10597.1</v>
+        <v>8784</v>
       </c>
       <c r="H551" s="13">
-        <v>5966.4</v>
+        <v>4834.5</v>
       </c>
       <c r="I551" s="13">
-        <v>4452.3</v>
+        <v>3571.2</v>
       </c>
       <c r="J551" s="13">
-        <v>2019.6</v>
+        <v>1661.9</v>
       </c>
       <c r="K551" s="13">
-        <v>1999.7</v>
+        <v>1632.7</v>
       </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.35">
@@ -19680,19 +19680,19 @@
         <v>37</v>
       </c>
       <c r="G552" s="13">
-        <v>773.1</v>
+        <v>631.4</v>
       </c>
       <c r="H552" s="13">
-        <v>576.20000000000005</v>
+        <v>496</v>
       </c>
       <c r="I552" s="13">
-        <v>274.7</v>
+        <v>232.4</v>
       </c>
       <c r="J552" s="13">
-        <v>1099.5999999999999</v>
+        <v>916.3</v>
       </c>
       <c r="K552" s="13">
-        <v>4228.2</v>
+        <v>3594.8</v>
       </c>
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.35">
@@ -19715,19 +19715,19 @@
         <v>13</v>
       </c>
       <c r="G553" s="13">
-        <v>44.2</v>
+        <v>33.6</v>
       </c>
       <c r="H553" s="13">
-        <v>206.7</v>
+        <v>183.5</v>
       </c>
       <c r="I553" s="13">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="J553" s="13">
-        <v>205</v>
+        <v>175.4</v>
       </c>
       <c r="K553" s="13">
-        <v>642.6</v>
+        <v>476.5</v>
       </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.35">
@@ -19785,19 +19785,19 @@
         <v>29</v>
       </c>
       <c r="G555" s="13">
-        <v>2753.3</v>
+        <v>2196.1999999999998</v>
       </c>
       <c r="H555" s="13">
-        <v>4141.3999999999996</v>
+        <v>3249.1</v>
       </c>
       <c r="I555" s="13">
-        <v>8905.7000000000007</v>
+        <v>6843.4</v>
       </c>
       <c r="J555" s="13">
-        <v>6924.4</v>
+        <v>5370.5</v>
       </c>
       <c r="K555" s="13">
-        <v>4885.1000000000004</v>
+        <v>3765.1</v>
       </c>
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.35">
@@ -19820,19 +19820,19 @@
         <v>37</v>
       </c>
       <c r="G556" s="13">
-        <v>960.3</v>
+        <v>782.1</v>
       </c>
       <c r="H556" s="13">
-        <v>1238.3</v>
+        <v>995.4</v>
       </c>
       <c r="I556" s="13">
-        <v>1577.9</v>
+        <v>1253.9000000000001</v>
       </c>
       <c r="J556" s="13">
-        <v>11683.1</v>
+        <v>9757.2999999999993</v>
       </c>
       <c r="K556" s="13">
-        <v>2541.6</v>
+        <v>2127.3000000000002</v>
       </c>
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.35">
@@ -19855,19 +19855,19 @@
         <v>13</v>
       </c>
       <c r="G557" s="13">
-        <v>84.9</v>
+        <v>70.8</v>
       </c>
       <c r="H557" s="13">
-        <v>55</v>
+        <v>45.1</v>
       </c>
       <c r="I557" s="13">
-        <v>65.099999999999994</v>
+        <v>54.6</v>
       </c>
       <c r="J557" s="13">
-        <v>74.599999999999994</v>
+        <v>61.9</v>
       </c>
       <c r="K557" s="13">
-        <v>43.9</v>
+        <v>37.799999999999997</v>
       </c>
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.35">
@@ -19890,19 +19890,19 @@
         <v>29</v>
       </c>
       <c r="G558" s="13">
-        <v>24371.1</v>
+        <v>19671.2</v>
       </c>
       <c r="H558" s="13">
-        <v>16780.099999999999</v>
+        <v>13572.9</v>
       </c>
       <c r="I558" s="13">
-        <v>16786.7</v>
+        <v>13435</v>
       </c>
       <c r="J558" s="13">
-        <v>10780.5</v>
+        <v>8791.6</v>
       </c>
       <c r="K558" s="13">
-        <v>10806.2</v>
+        <v>8805.1</v>
       </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.35">
@@ -19925,19 +19925,19 @@
         <v>37</v>
       </c>
       <c r="G559" s="13">
-        <v>294.2</v>
+        <v>266.3</v>
       </c>
       <c r="H559" s="13">
-        <v>867.2</v>
+        <v>793.8</v>
       </c>
       <c r="I559" s="13">
-        <v>555.4</v>
+        <v>506.5</v>
       </c>
       <c r="J559" s="13">
-        <v>810.9</v>
+        <v>674.8</v>
       </c>
       <c r="K559" s="13">
-        <v>2936.3</v>
+        <v>2576.3000000000002</v>
       </c>
     </row>
     <row r="560" spans="1:11" x14ac:dyDescent="0.35">
@@ -19960,19 +19960,19 @@
         <v>13</v>
       </c>
       <c r="G560" s="13">
-        <v>11680.3</v>
+        <v>8795.2000000000007</v>
       </c>
       <c r="H560" s="13">
-        <v>10457.200000000001</v>
+        <v>7756.9</v>
       </c>
       <c r="I560" s="13">
-        <v>9474.1</v>
+        <v>6981.5</v>
       </c>
       <c r="J560" s="13">
-        <v>9249</v>
+        <v>6868</v>
       </c>
       <c r="K560" s="13">
-        <v>8886.2999999999993</v>
+        <v>6515.6</v>
       </c>
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.35">
@@ -19995,19 +19995,19 @@
         <v>17</v>
       </c>
       <c r="G561" s="13">
-        <v>39.700000000000003</v>
+        <v>35.6</v>
       </c>
       <c r="H561" s="13">
-        <v>248</v>
+        <v>217.8</v>
       </c>
       <c r="I561" s="13">
-        <v>1209.5</v>
+        <v>1037.9000000000001</v>
       </c>
       <c r="J561" s="13">
-        <v>577</v>
+        <v>456.3</v>
       </c>
       <c r="K561" s="13">
-        <v>96.3</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.35">
@@ -20030,16 +20030,16 @@
         <v>18</v>
       </c>
       <c r="G562" s="13">
-        <v>2.7</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H562" s="13">
         <v>0</v>
       </c>
       <c r="I562" s="13">
-        <v>2.7</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J562" s="13">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K562" s="13">
         <v>0</v>
@@ -20065,19 +20065,19 @@
         <v>29</v>
       </c>
       <c r="G563" s="13">
-        <v>16197.7</v>
+        <v>13715.2</v>
       </c>
       <c r="H563" s="13">
-        <v>10358.6</v>
+        <v>8637</v>
       </c>
       <c r="I563" s="13">
-        <v>11757.3</v>
+        <v>9559.1</v>
       </c>
       <c r="J563" s="13">
-        <v>12656.5</v>
+        <v>11078.5</v>
       </c>
       <c r="K563" s="13">
-        <v>16942</v>
+        <v>13881.5</v>
       </c>
     </row>
     <row r="564" spans="1:11" x14ac:dyDescent="0.35">
@@ -20100,19 +20100,19 @@
         <v>37</v>
       </c>
       <c r="G564" s="13">
-        <v>31.2</v>
+        <v>27.4</v>
       </c>
       <c r="H564" s="13">
-        <v>57</v>
+        <v>52.7</v>
       </c>
       <c r="I564" s="13">
-        <v>113.9</v>
+        <v>104.1</v>
       </c>
       <c r="J564" s="13">
-        <v>48.9</v>
+        <v>42.8</v>
       </c>
       <c r="K564" s="13">
-        <v>1132.7</v>
+        <v>957.9</v>
       </c>
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.35">
@@ -20135,19 +20135,19 @@
         <v>13</v>
       </c>
       <c r="G565" s="13">
-        <v>993.5</v>
+        <v>770.2</v>
       </c>
       <c r="H565" s="13">
-        <v>814.8</v>
+        <v>607.9</v>
       </c>
       <c r="I565" s="13">
-        <v>3136.4</v>
+        <v>2276.8000000000002</v>
       </c>
       <c r="J565" s="13">
-        <v>1457.5</v>
+        <v>1103</v>
       </c>
       <c r="K565" s="13">
-        <v>1716.7</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.35">
@@ -20170,19 +20170,19 @@
         <v>29</v>
       </c>
       <c r="G566" s="13">
-        <v>11048.9</v>
+        <v>8562</v>
       </c>
       <c r="H566" s="13">
-        <v>14245.4</v>
+        <v>11014</v>
       </c>
       <c r="I566" s="13">
-        <v>15435.5</v>
+        <v>11852.3</v>
       </c>
       <c r="J566" s="13">
-        <v>17297.2</v>
+        <v>13369.2</v>
       </c>
       <c r="K566" s="13">
-        <v>21313.8</v>
+        <v>16513.099999999999</v>
       </c>
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.35">
@@ -20205,19 +20205,19 @@
         <v>37</v>
       </c>
       <c r="G567" s="13">
-        <v>22.7</v>
+        <v>21.7</v>
       </c>
       <c r="H567" s="13">
-        <v>719.6</v>
+        <v>636.1</v>
       </c>
       <c r="I567" s="13">
-        <v>298.5</v>
+        <v>255.7</v>
       </c>
       <c r="J567" s="13">
-        <v>1467.3</v>
+        <v>1244.7</v>
       </c>
       <c r="K567" s="13">
-        <v>801.1</v>
+        <v>717.9</v>
       </c>
     </row>
     <row r="568" spans="1:11" x14ac:dyDescent="0.35">
@@ -20240,19 +20240,19 @@
         <v>13</v>
       </c>
       <c r="G568" s="13">
-        <v>4347.7</v>
+        <v>3458.3</v>
       </c>
       <c r="H568" s="13">
-        <v>1390.3</v>
+        <v>1090.0999999999999</v>
       </c>
       <c r="I568" s="13">
-        <v>488.9</v>
+        <v>384.9</v>
       </c>
       <c r="J568" s="13">
-        <v>287.7</v>
+        <v>234.9</v>
       </c>
       <c r="K568" s="13">
-        <v>38</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="569" spans="1:11" x14ac:dyDescent="0.35">
@@ -20275,19 +20275,19 @@
         <v>29</v>
       </c>
       <c r="G569" s="13">
-        <v>7541.6</v>
+        <v>6267.9</v>
       </c>
       <c r="H569" s="13">
-        <v>4953.6000000000004</v>
+        <v>4078.4</v>
       </c>
       <c r="I569" s="13">
-        <v>4748.3999999999996</v>
+        <v>3890.6</v>
       </c>
       <c r="J569" s="13">
-        <v>2871.8</v>
+        <v>2491.1999999999998</v>
       </c>
       <c r="K569" s="13">
-        <v>4135.1000000000004</v>
+        <v>3435.8</v>
       </c>
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.35">
@@ -20310,7 +20310,7 @@
         <v>37</v>
       </c>
       <c r="G570" s="13">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H570" s="13">
         <v>0</v>
